--- a/grupos/3BEM - Estadisticos 20211.xlsx
+++ b/grupos/3BEM - Estadisticos 20211.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="503" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="279" uniqueCount="144">
   <si>
     <t>Materia</t>
   </si>
@@ -179,21 +179,21 @@
     <t>Rodríguez Román Leticia</t>
   </si>
   <si>
+    <t>Molina Quezada Raúl</t>
+  </si>
+  <si>
+    <t>Cruz Alejo José Armando</t>
+  </si>
+  <si>
     <t>Avila Coronado Julieta</t>
   </si>
   <si>
-    <t>Molina Quezada Raúl</t>
-  </si>
-  <si>
     <t>Camarillo Aburto Raymundo</t>
   </si>
   <si>
     <t>Aurioles Maldonado Luis Gustavo</t>
   </si>
   <si>
-    <t>Cruz Alejo José Armando</t>
-  </si>
-  <si>
     <t>NC</t>
   </si>
   <si>
@@ -206,6 +206,45 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>DE JESUS</t>
+  </si>
+  <si>
+    <t>MENDIZABAL</t>
+  </si>
+  <si>
+    <t>NUBE</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>XOTLANIHUA</t>
+  </si>
+  <si>
+    <t>EVARISTO</t>
+  </si>
+  <si>
+    <t>ALEMAN</t>
+  </si>
+  <si>
+    <t>TEXCAHUA</t>
+  </si>
+  <si>
+    <t>ALDAIR ALAN</t>
+  </si>
+  <si>
+    <t>ALDER ALBERTO</t>
+  </si>
+  <si>
+    <t>CHRISTIAN YAIR</t>
+  </si>
+  <si>
+    <t>ROSA ISELA</t>
+  </si>
+  <si>
+    <t>ALEXANDER</t>
+  </si>
+  <si>
     <t>ALVAREZ</t>
   </si>
   <si>
@@ -215,12 +254,27 @@
     <t>ANASTACIO</t>
   </si>
   <si>
+    <t>AGUILAR</t>
+  </si>
+  <si>
+    <t>BERNARDO</t>
+  </si>
+  <si>
+    <t>CITALAN</t>
+  </si>
+  <si>
     <t>CID</t>
   </si>
   <si>
+    <t>COLOHUA</t>
+  </si>
+  <si>
     <t>DE LA CRUZ</t>
   </si>
   <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
     <t>DIAZ</t>
   </si>
   <si>
@@ -233,19 +287,28 @@
     <t>GONZALEZ</t>
   </si>
   <si>
-    <t>DE JESUS</t>
-  </si>
-  <si>
-    <t>MENDIZABAL</t>
+    <t>GOMEZ</t>
+  </si>
+  <si>
+    <t>GUEVARA</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
   </si>
   <si>
     <t>NAJERA</t>
   </si>
   <si>
-    <t>NUBE</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
+    <t>ORTIZ</t>
+  </si>
+  <si>
+    <t>OLMOS</t>
+  </si>
+  <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
   </si>
   <si>
     <t>TELLEZ</t>
@@ -257,9 +320,6 @@
     <t>VASQUEZ</t>
   </si>
   <si>
-    <t>XOTLANIHUA</t>
-  </si>
-  <si>
     <t>CONCHE</t>
   </si>
   <si>
@@ -269,9 +329,21 @@
     <t>ROMERO</t>
   </si>
   <si>
+    <t>GARCÍA</t>
+  </si>
+  <si>
+    <t>CONCHOA</t>
+  </si>
+  <si>
+    <t>ROMANOS</t>
+  </si>
+  <si>
     <t>VALENCIA</t>
   </si>
   <si>
+    <t>MARROQUIN</t>
+  </si>
+  <si>
     <t>VAZQUEZ</t>
   </si>
   <si>
@@ -281,10 +353,19 @@
     <t>MARTINEZ</t>
   </si>
   <si>
-    <t>EVARISTO</t>
-  </si>
-  <si>
-    <t>ALEMAN</t>
+    <t>HERRERA</t>
+  </si>
+  <si>
+    <t>VELAZQUEZ</t>
+  </si>
+  <si>
+    <t>MARCELINO</t>
+  </si>
+  <si>
+    <t>ROSETE</t>
+  </si>
+  <si>
+    <t>ROBLES</t>
   </si>
   <si>
     <t>GAMEZ</t>
@@ -293,9 +374,6 @@
     <t>PEREZ</t>
   </si>
   <si>
-    <t>TEXCAHUA</t>
-  </si>
-  <si>
     <t>GUSTAVO</t>
   </si>
   <si>
@@ -305,9 +383,21 @@
     <t>HIRAM FABIAN</t>
   </si>
   <si>
+    <t>RAUL</t>
+  </si>
+  <si>
+    <t>URIEL</t>
+  </si>
+  <si>
+    <t>MISAEL</t>
+  </si>
+  <si>
     <t>JESUS</t>
   </si>
   <si>
+    <t>DAVID</t>
+  </si>
+  <si>
     <t>YAHIR</t>
   </si>
   <si>
@@ -323,10 +413,16 @@
     <t>MARCO ANTONIO</t>
   </si>
   <si>
-    <t>ALDAIR ALAN</t>
-  </si>
-  <si>
-    <t>ALDER ALBERTO</t>
+    <t>ROBERTO</t>
+  </si>
+  <si>
+    <t>NOEL ALBERTO</t>
+  </si>
+  <si>
+    <t>LUIS ALBERTO</t>
+  </si>
+  <si>
+    <t>ADRIAN</t>
   </si>
   <si>
     <t>ELI ANTONIO</t>
@@ -335,10 +431,16 @@
     <t>ISAAC</t>
   </si>
   <si>
-    <t>CHRISTIAN YAIR</t>
-  </si>
-  <si>
-    <t>ROSA ISELA</t>
+    <t>SERGIO MARIANO</t>
+  </si>
+  <si>
+    <t>IVAN</t>
+  </si>
+  <si>
+    <t>JUAN CARLOS</t>
+  </si>
+  <si>
+    <t>CESAR OMAR</t>
   </si>
   <si>
     <t>BENY ALEXANDER</t>
@@ -348,108 +450,6 @@
   </si>
   <si>
     <t>GUILLERMO</t>
-  </si>
-  <si>
-    <t>ALEXANDER</t>
-  </si>
-  <si>
-    <t>AGUILAR</t>
-  </si>
-  <si>
-    <t>BERNARDO</t>
-  </si>
-  <si>
-    <t>CITALAN</t>
-  </si>
-  <si>
-    <t>COLOHUA</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>GOMEZ</t>
-  </si>
-  <si>
-    <t>GUEVARA</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>ORTIZ</t>
-  </si>
-  <si>
-    <t>OLMOS</t>
-  </si>
-  <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>GARCÍA</t>
-  </si>
-  <si>
-    <t>CONCHOA</t>
-  </si>
-  <si>
-    <t>ROMANOS</t>
-  </si>
-  <si>
-    <t>MARROQUIN</t>
-  </si>
-  <si>
-    <t>HERRERA</t>
-  </si>
-  <si>
-    <t>VELAZQUEZ</t>
-  </si>
-  <si>
-    <t>MARCELINO</t>
-  </si>
-  <si>
-    <t>ROSETE</t>
-  </si>
-  <si>
-    <t>ROBLES</t>
-  </si>
-  <si>
-    <t>RAUL</t>
-  </si>
-  <si>
-    <t>URIEL</t>
-  </si>
-  <si>
-    <t>MISAEL</t>
-  </si>
-  <si>
-    <t>DAVID</t>
-  </si>
-  <si>
-    <t>ROBERTO</t>
-  </si>
-  <si>
-    <t>NOEL ALBERTO</t>
-  </si>
-  <si>
-    <t>LUIS ALBERTO</t>
-  </si>
-  <si>
-    <t>ADRIAN</t>
-  </si>
-  <si>
-    <t>SERGIO MARIANO</t>
-  </si>
-  <si>
-    <t>IVAN</t>
-  </si>
-  <si>
-    <t>JUAN CARLOS</t>
-  </si>
-  <si>
-    <t>CESAR OMAR</t>
   </si>
 </sst>
 </file>
@@ -953,22 +953,22 @@
         <v>10</v>
       </c>
       <c r="H4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N4">
         <v>-1</v>
@@ -989,16 +989,16 @@
         <v>-1</v>
       </c>
       <c r="T4">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="U4">
         <v>7</v>
       </c>
       <c r="V4">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W4">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X4">
         <v>10</v>
@@ -1015,10 +1015,10 @@
         <v>5</v>
       </c>
       <c r="C5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E5">
         <v>7</v>
@@ -1030,22 +1030,22 @@
         <v>10</v>
       </c>
       <c r="H5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I5">
         <v>-1</v>
       </c>
       <c r="J5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N5">
         <v>-1</v>
@@ -1069,13 +1069,13 @@
         <v>5</v>
       </c>
       <c r="U5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W5">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X5">
         <v>9</v>
@@ -1095,7 +1095,7 @@
         <v>6</v>
       </c>
       <c r="D6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="E6">
         <v>6</v>
@@ -1107,22 +1107,22 @@
         <v>10</v>
       </c>
       <c r="H6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N6">
         <v>-1</v>
@@ -1143,19 +1143,19 @@
         <v>-1</v>
       </c>
       <c r="T6">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="U6">
         <v>6</v>
       </c>
       <c r="V6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W6">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y6">
         <v>10</v>
@@ -1169,7 +1169,7 @@
         <v>6</v>
       </c>
       <c r="C7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D7">
         <v>7</v>
@@ -1181,25 +1181,25 @@
         <v>10</v>
       </c>
       <c r="G7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="H7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N7">
         <v>-1</v>
@@ -1223,10 +1223,10 @@
         <v>6</v>
       </c>
       <c r="U7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W7">
         <v>7</v>
@@ -1235,7 +1235,7 @@
         <v>10</v>
       </c>
       <c r="Y7">
-        <v>-1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8" spans="1:25">
@@ -1261,22 +1261,22 @@
         <v>10</v>
       </c>
       <c r="H8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N8">
         <v>-1</v>
@@ -1297,7 +1297,7 @@
         <v>-1</v>
       </c>
       <c r="T8">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U8">
         <v>6</v>
@@ -1306,13 +1306,13 @@
         <v>9</v>
       </c>
       <c r="W8">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X8">
         <v>10</v>
       </c>
       <c r="Y8">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9" spans="1:25">
@@ -1323,7 +1323,7 @@
         <v>6</v>
       </c>
       <c r="C9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D9">
         <v>9</v>
@@ -1338,19 +1338,19 @@
         <v>10</v>
       </c>
       <c r="H9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I9">
         <v>-1</v>
       </c>
       <c r="J9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M9">
         <v>-1</v>
@@ -1374,16 +1374,16 @@
         <v>-1</v>
       </c>
       <c r="T9">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="U9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V9">
         <v>9</v>
       </c>
       <c r="W9">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X9">
         <v>10</v>
@@ -1415,22 +1415,22 @@
         <v>10</v>
       </c>
       <c r="H10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N10">
         <v>-1</v>
@@ -1454,13 +1454,13 @@
         <v>10</v>
       </c>
       <c r="U10">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V10">
         <v>10</v>
       </c>
       <c r="W10">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X10">
         <v>10</v>
@@ -1492,22 +1492,22 @@
         <v>10</v>
       </c>
       <c r="H11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N11">
         <v>-1</v>
@@ -1528,7 +1528,7 @@
         <v>-1</v>
       </c>
       <c r="T11">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U11">
         <v>7</v>
@@ -1537,7 +1537,7 @@
         <v>10</v>
       </c>
       <c r="W11">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X11">
         <v>10</v>
@@ -1569,22 +1569,22 @@
         <v>10</v>
       </c>
       <c r="H12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N12">
         <v>-1</v>
@@ -1611,7 +1611,7 @@
         <v>7</v>
       </c>
       <c r="V12">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W12">
         <v>10</v>
@@ -1631,13 +1631,13 @@
         <v>5</v>
       </c>
       <c r="C13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F13">
         <v>10</v>
@@ -1646,19 +1646,19 @@
         <v>-1</v>
       </c>
       <c r="H13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I13">
         <v>-1</v>
       </c>
       <c r="J13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M13">
         <v>-1</v>
@@ -1685,13 +1685,13 @@
         <v>5</v>
       </c>
       <c r="U13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X13">
         <v>10</v>
@@ -1708,37 +1708,37 @@
         <v>5</v>
       </c>
       <c r="C14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F14">
         <v>10</v>
       </c>
       <c r="G14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="H14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N14">
         <v>-1</v>
@@ -1759,22 +1759,22 @@
         <v>-1</v>
       </c>
       <c r="T14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X14">
         <v>10</v>
       </c>
       <c r="Y14">
-        <v>-1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15" spans="1:25">
@@ -1785,37 +1785,37 @@
         <v>5</v>
       </c>
       <c r="C15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="E15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F15">
         <v>9</v>
       </c>
       <c r="G15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="H15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N15">
         <v>-1</v>
@@ -1836,22 +1836,22 @@
         <v>-1</v>
       </c>
       <c r="T15">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="U15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X15">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y15">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="16" spans="1:25">
@@ -1862,37 +1862,37 @@
         <v>5</v>
       </c>
       <c r="C16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F16">
         <v>10</v>
       </c>
       <c r="G16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="H16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I16">
         <v>-1</v>
       </c>
       <c r="J16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N16">
         <v>-1</v>
@@ -1913,22 +1913,22 @@
         <v>-1</v>
       </c>
       <c r="T16">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X16">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y16">
-        <v>-1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17" spans="1:25">
@@ -1942,7 +1942,7 @@
         <v>7</v>
       </c>
       <c r="D17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="E17">
         <v>10</v>
@@ -1954,22 +1954,22 @@
         <v>10</v>
       </c>
       <c r="H17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N17">
         <v>-1</v>
@@ -1990,13 +1990,13 @@
         <v>-1</v>
       </c>
       <c r="T17">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U17">
         <v>7</v>
       </c>
       <c r="V17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W17">
         <v>10</v>
@@ -2031,22 +2031,22 @@
         <v>10</v>
       </c>
       <c r="H18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N18">
         <v>-1</v>
@@ -2070,13 +2070,13 @@
         <v>10</v>
       </c>
       <c r="U18">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V18">
         <v>9</v>
       </c>
       <c r="W18">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X18">
         <v>10</v>
@@ -2093,37 +2093,37 @@
         <v>5</v>
       </c>
       <c r="C19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="E19">
         <v>6</v>
       </c>
       <c r="F19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="G19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N19">
         <v>-1</v>
@@ -2144,22 +2144,22 @@
         <v>-1</v>
       </c>
       <c r="T19">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="U19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W19">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y19">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="20" spans="1:25">
@@ -2185,22 +2185,22 @@
         <v>10</v>
       </c>
       <c r="H20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I20">
         <v>-1</v>
       </c>
       <c r="J20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N20">
         <v>-1</v>
@@ -2221,7 +2221,7 @@
         <v>-1</v>
       </c>
       <c r="T20">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="U20">
         <v>9</v>
@@ -2262,22 +2262,22 @@
         <v>10</v>
       </c>
       <c r="H21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N21">
         <v>-1</v>
@@ -2298,7 +2298,7 @@
         <v>-1</v>
       </c>
       <c r="T21">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U21">
         <v>7</v>
@@ -2339,22 +2339,22 @@
         <v>10</v>
       </c>
       <c r="H22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N22">
         <v>-1</v>
@@ -2375,7 +2375,7 @@
         <v>-1</v>
       </c>
       <c r="T22">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U22">
         <v>7</v>
@@ -2384,13 +2384,13 @@
         <v>10</v>
       </c>
       <c r="W22">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="X22">
         <v>10</v>
       </c>
       <c r="Y22">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="23" spans="1:25">
@@ -2401,37 +2401,37 @@
         <v>5</v>
       </c>
       <c r="C23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="H23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I23">
         <v>-1</v>
       </c>
       <c r="J23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N23">
         <v>-1</v>
@@ -2455,19 +2455,19 @@
         <v>5</v>
       </c>
       <c r="U23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y23">
-        <v>-1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="24" spans="1:25">
@@ -2478,37 +2478,37 @@
         <v>5</v>
       </c>
       <c r="C24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="H24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I24">
         <v>-1</v>
       </c>
       <c r="J24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N24">
         <v>-1</v>
@@ -2532,19 +2532,19 @@
         <v>5</v>
       </c>
       <c r="U24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y24">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="25" spans="1:25">
@@ -2555,34 +2555,34 @@
         <v>8</v>
       </c>
       <c r="C25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E25">
         <v>7</v>
       </c>
       <c r="F25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G25">
         <v>-1</v>
       </c>
       <c r="H25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I25">
         <v>-1</v>
       </c>
       <c r="J25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M25">
         <v>-1</v>
@@ -2606,19 +2606,19 @@
         <v>-1</v>
       </c>
       <c r="T25">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W25">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y25">
         <v>-1</v>
@@ -2647,19 +2647,19 @@
         <v>10</v>
       </c>
       <c r="H26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M26">
         <v>-1</v>
@@ -2683,13 +2683,13 @@
         <v>-1</v>
       </c>
       <c r="T26">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U26">
         <v>8</v>
       </c>
       <c r="V26">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W26">
         <v>9</v>
@@ -2724,22 +2724,22 @@
         <v>10</v>
       </c>
       <c r="H27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N27">
         <v>-1</v>
@@ -2766,7 +2766,7 @@
         <v>7</v>
       </c>
       <c r="V27">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W27">
         <v>9</v>
@@ -2801,22 +2801,22 @@
         <v>10</v>
       </c>
       <c r="H28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N28">
         <v>-1</v>
@@ -2837,7 +2837,7 @@
         <v>-1</v>
       </c>
       <c r="T28">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U28">
         <v>7</v>
@@ -2846,7 +2846,7 @@
         <v>10</v>
       </c>
       <c r="W28">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X28">
         <v>10</v>
@@ -2878,22 +2878,22 @@
         <v>10</v>
       </c>
       <c r="H29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N29">
         <v>-1</v>
@@ -2914,10 +2914,10 @@
         <v>-1</v>
       </c>
       <c r="T29">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U29">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V29">
         <v>9</v>
@@ -2940,10 +2940,10 @@
         <v>5</v>
       </c>
       <c r="C30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E30">
         <v>8</v>
@@ -2955,19 +2955,19 @@
         <v>-1</v>
       </c>
       <c r="H30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M30">
         <v>-1</v>
@@ -2991,13 +2991,13 @@
         <v>-1</v>
       </c>
       <c r="T30">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W30">
         <v>8</v>
@@ -3017,34 +3017,34 @@
         <v>6</v>
       </c>
       <c r="C31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E31">
         <v>6</v>
       </c>
       <c r="F31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G31">
         <v>10</v>
       </c>
       <c r="H31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I31">
         <v>-1</v>
       </c>
       <c r="J31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M31">
         <v>-1</v>
@@ -3071,16 +3071,16 @@
         <v>6</v>
       </c>
       <c r="U31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W31">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y31">
         <v>10</v>
@@ -3094,7 +3094,7 @@
         <v>6</v>
       </c>
       <c r="C32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D32">
         <v>8</v>
@@ -3109,22 +3109,22 @@
         <v>10</v>
       </c>
       <c r="H32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N32">
         <v>-1</v>
@@ -3145,19 +3145,19 @@
         <v>-1</v>
       </c>
       <c r="T32">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="U32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V32">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W32">
         <v>9</v>
       </c>
       <c r="X32">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y32">
         <v>10</v>
@@ -3180,28 +3180,28 @@
         <v>8</v>
       </c>
       <c r="F33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="G33">
         <v>10</v>
       </c>
       <c r="H33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N33">
         <v>-1</v>
@@ -3222,7 +3222,7 @@
         <v>-1</v>
       </c>
       <c r="T33">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="U33">
         <v>7</v>
@@ -3234,10 +3234,10 @@
         <v>8</v>
       </c>
       <c r="X33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y33">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="34" spans="1:25">
@@ -3263,19 +3263,19 @@
         <v>-1</v>
       </c>
       <c r="H34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M34">
         <v>-1</v>
@@ -3311,7 +3311,7 @@
         <v>8</v>
       </c>
       <c r="X34">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y34">
         <v>-1</v>
@@ -3379,30 +3379,30 @@
         <v>32</v>
       </c>
       <c r="D2">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="E2">
+        <v>10</v>
+      </c>
+      <c r="F2">
+        <v>68.75</v>
+      </c>
+      <c r="G2">
+        <v>31.25</v>
+      </c>
+      <c r="H2">
+        <v>6.4</v>
+      </c>
+      <c r="I2">
         <v>0</v>
       </c>
-      <c r="F2">
-        <v>53.13</v>
-      </c>
-      <c r="G2">
+      <c r="J2">
         <v>0</v>
-      </c>
-      <c r="H2">
-        <v>7.1</v>
-      </c>
-      <c r="I2">
-        <v>15</v>
-      </c>
-      <c r="J2">
-        <v>46.88</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B3" t="s">
         <v>53</v>
@@ -3411,30 +3411,30 @@
         <v>32</v>
       </c>
       <c r="D3">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="E3">
         <v>0</v>
       </c>
       <c r="F3">
-        <v>59.38</v>
+        <v>84.38</v>
       </c>
       <c r="G3">
         <v>0</v>
       </c>
       <c r="H3">
-        <v>9</v>
+        <v>9.5</v>
       </c>
       <c r="I3">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="J3">
-        <v>40.63</v>
+        <v>15.63</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B4" t="s">
         <v>54</v>
@@ -3443,30 +3443,30 @@
         <v>32</v>
       </c>
       <c r="D4">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="E4">
+        <v>5</v>
+      </c>
+      <c r="F4">
+        <v>84.38</v>
+      </c>
+      <c r="G4">
+        <v>15.63</v>
+      </c>
+      <c r="H4">
+        <v>7.7</v>
+      </c>
+      <c r="I4">
         <v>0</v>
       </c>
-      <c r="F4">
-        <v>62.5</v>
-      </c>
-      <c r="G4">
+      <c r="J4">
         <v>0</v>
-      </c>
-      <c r="H4">
-        <v>10</v>
-      </c>
-      <c r="I4">
-        <v>12</v>
-      </c>
-      <c r="J4">
-        <v>37.5</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B5" t="s">
         <v>55</v>
@@ -3475,19 +3475,19 @@
         <v>32</v>
       </c>
       <c r="D5">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="E5">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="F5">
-        <v>68.75</v>
+        <v>87.5</v>
       </c>
       <c r="G5">
-        <v>31.25</v>
+        <v>12.5</v>
       </c>
       <c r="H5">
-        <v>6.8</v>
+        <v>8</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -3498,7 +3498,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B6" t="s">
         <v>56</v>
@@ -3507,30 +3507,30 @@
         <v>32</v>
       </c>
       <c r="D6">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="E6">
+        <v>4</v>
+      </c>
+      <c r="F6">
+        <v>87.5</v>
+      </c>
+      <c r="G6">
+        <v>12.5</v>
+      </c>
+      <c r="H6">
+        <v>7.8</v>
+      </c>
+      <c r="I6">
         <v>0</v>
       </c>
-      <c r="F6">
-        <v>78.13</v>
-      </c>
-      <c r="G6">
+      <c r="J6">
         <v>0</v>
-      </c>
-      <c r="H6">
-        <v>9.6</v>
-      </c>
-      <c r="I6">
-        <v>7</v>
-      </c>
-      <c r="J6">
-        <v>21.88</v>
       </c>
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B7" t="s">
         <v>57</v>
@@ -3539,25 +3539,25 @@
         <v>32</v>
       </c>
       <c r="D7">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="E7">
         <v>0</v>
       </c>
       <c r="F7">
-        <v>81.25</v>
+        <v>100</v>
       </c>
       <c r="G7">
         <v>0</v>
       </c>
       <c r="H7">
-        <v>8.199999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="I7">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J7">
-        <v>18.75</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -3567,7 +3567,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F54"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -3596,39 +3596,36 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2">
-        <v>20330051920039</v>
+        <v>20330051920097</v>
       </c>
       <c r="B2" t="s">
         <v>62</v>
       </c>
       <c r="C2" t="s">
-        <v>80</v>
+        <v>67</v>
       </c>
       <c r="D2" t="s">
-        <v>92</v>
+        <v>70</v>
       </c>
       <c r="E2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="3" spans="1:6">
       <c r="A3">
-        <v>20330051920039</v>
+        <v>20330051920099</v>
       </c>
       <c r="B3" t="s">
-        <v>62</v>
-      </c>
-      <c r="C3" t="s">
-        <v>80</v>
+        <v>63</v>
       </c>
       <c r="D3" t="s">
-        <v>92</v>
+        <v>71</v>
       </c>
       <c r="E3" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F3" t="s">
         <v>53</v>
@@ -3636,19 +3633,19 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4">
-        <v>20330051920040</v>
+        <v>20330051920100</v>
       </c>
       <c r="B4" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C4" t="s">
-        <v>81</v>
+        <v>68</v>
       </c>
       <c r="D4" t="s">
-        <v>93</v>
+        <v>72</v>
       </c>
       <c r="E4" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F4" t="s">
         <v>53</v>
@@ -3656,993 +3653,42 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5">
-        <v>20330051920042</v>
+        <v>20330051920107</v>
       </c>
       <c r="B5" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C5" t="s">
-        <v>82</v>
+        <v>65</v>
       </c>
       <c r="D5" t="s">
-        <v>94</v>
+        <v>73</v>
       </c>
       <c r="E5" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6">
-        <v>20330051920042</v>
+        <v>20330051920113</v>
       </c>
       <c r="B6" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C6" t="s">
-        <v>82</v>
+        <v>69</v>
       </c>
       <c r="D6" t="s">
-        <v>94</v>
+        <v>74</v>
       </c>
       <c r="E6" t="s">
         <v>10</v>
       </c>
       <c r="F6" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7">
-        <v>20330051920046</v>
-      </c>
-      <c r="B7" t="s">
-        <v>65</v>
-      </c>
-      <c r="C7" t="s">
-        <v>83</v>
-      </c>
-      <c r="D7" t="s">
-        <v>95</v>
-      </c>
-      <c r="E7" t="s">
-        <v>6</v>
-      </c>
-      <c r="F7" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8">
-        <v>20330051920050</v>
-      </c>
-      <c r="B8" t="s">
-        <v>66</v>
-      </c>
-      <c r="C8" t="s">
-        <v>71</v>
-      </c>
-      <c r="D8" t="s">
-        <v>96</v>
-      </c>
-      <c r="E8" t="s">
-        <v>6</v>
-      </c>
-      <c r="F8" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9">
-        <v>20330051920050</v>
-      </c>
-      <c r="B9" t="s">
-        <v>66</v>
-      </c>
-      <c r="C9" t="s">
-        <v>71</v>
-      </c>
-      <c r="D9" t="s">
-        <v>96</v>
-      </c>
-      <c r="E9" t="s">
-        <v>7</v>
-      </c>
-      <c r="F9" t="s">
         <v>53</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10">
-        <v>20330051920050</v>
-      </c>
-      <c r="B10" t="s">
-        <v>66</v>
-      </c>
-      <c r="C10" t="s">
-        <v>71</v>
-      </c>
-      <c r="D10" t="s">
-        <v>96</v>
-      </c>
-      <c r="E10" t="s">
-        <v>10</v>
-      </c>
-      <c r="F10" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11">
-        <v>20330051920050</v>
-      </c>
-      <c r="B11" t="s">
-        <v>66</v>
-      </c>
-      <c r="C11" t="s">
-        <v>71</v>
-      </c>
-      <c r="D11" t="s">
-        <v>96</v>
-      </c>
-      <c r="E11" t="s">
-        <v>8</v>
-      </c>
-      <c r="F11" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12">
-        <v>20330051920365</v>
-      </c>
-      <c r="B12" t="s">
-        <v>67</v>
-      </c>
-      <c r="C12" t="s">
-        <v>84</v>
-      </c>
-      <c r="D12" t="s">
-        <v>97</v>
-      </c>
-      <c r="E12" t="s">
-        <v>6</v>
-      </c>
-      <c r="F12" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13">
-        <v>20330051920365</v>
-      </c>
-      <c r="B13" t="s">
-        <v>67</v>
-      </c>
-      <c r="C13" t="s">
-        <v>84</v>
-      </c>
-      <c r="D13" t="s">
-        <v>97</v>
-      </c>
-      <c r="E13" t="s">
-        <v>7</v>
-      </c>
-      <c r="F13" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14">
-        <v>20330051920365</v>
-      </c>
-      <c r="B14" t="s">
-        <v>67</v>
-      </c>
-      <c r="C14" t="s">
-        <v>84</v>
-      </c>
-      <c r="D14" t="s">
-        <v>97</v>
-      </c>
-      <c r="E14" t="s">
-        <v>10</v>
-      </c>
-      <c r="F14" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15">
-        <v>20330051920365</v>
-      </c>
-      <c r="B15" t="s">
-        <v>67</v>
-      </c>
-      <c r="C15" t="s">
-        <v>84</v>
-      </c>
-      <c r="D15" t="s">
-        <v>97</v>
-      </c>
-      <c r="E15" t="s">
-        <v>8</v>
-      </c>
-      <c r="F15" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16">
-        <v>20330051920052</v>
-      </c>
-      <c r="B16" t="s">
-        <v>68</v>
-      </c>
-      <c r="C16" t="s">
-        <v>85</v>
-      </c>
-      <c r="D16" t="s">
-        <v>98</v>
-      </c>
-      <c r="E16" t="s">
-        <v>6</v>
-      </c>
-      <c r="F16" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
-      <c r="A17">
-        <v>20330051920052</v>
-      </c>
-      <c r="B17" t="s">
-        <v>68</v>
-      </c>
-      <c r="C17" t="s">
-        <v>85</v>
-      </c>
-      <c r="D17" t="s">
-        <v>98</v>
-      </c>
-      <c r="E17" t="s">
-        <v>7</v>
-      </c>
-      <c r="F17" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
-      <c r="A18">
-        <v>20330051920052</v>
-      </c>
-      <c r="B18" t="s">
-        <v>68</v>
-      </c>
-      <c r="C18" t="s">
-        <v>85</v>
-      </c>
-      <c r="D18" t="s">
-        <v>98</v>
-      </c>
-      <c r="E18" t="s">
-        <v>10</v>
-      </c>
-      <c r="F18" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6">
-      <c r="A19">
-        <v>20330051920052</v>
-      </c>
-      <c r="B19" t="s">
-        <v>68</v>
-      </c>
-      <c r="C19" t="s">
-        <v>85</v>
-      </c>
-      <c r="D19" t="s">
-        <v>98</v>
-      </c>
-      <c r="E19" t="s">
-        <v>8</v>
-      </c>
-      <c r="F19" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6">
-      <c r="A20">
-        <v>20330051920053</v>
-      </c>
-      <c r="B20" t="s">
-        <v>69</v>
-      </c>
-      <c r="C20" t="s">
-        <v>86</v>
-      </c>
-      <c r="D20" t="s">
-        <v>99</v>
-      </c>
-      <c r="E20" t="s">
-        <v>7</v>
-      </c>
-      <c r="F20" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6">
-      <c r="A21">
-        <v>20330051920055</v>
-      </c>
-      <c r="B21" t="s">
-        <v>70</v>
-      </c>
-      <c r="C21" t="s">
-        <v>68</v>
-      </c>
-      <c r="D21" t="s">
-        <v>100</v>
-      </c>
-      <c r="E21" t="s">
-        <v>6</v>
-      </c>
-      <c r="F21" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6">
-      <c r="A22">
-        <v>20330051920055</v>
-      </c>
-      <c r="B22" t="s">
-        <v>70</v>
-      </c>
-      <c r="C22" t="s">
-        <v>68</v>
-      </c>
-      <c r="D22" t="s">
-        <v>100</v>
-      </c>
-      <c r="E22" t="s">
-        <v>7</v>
-      </c>
-      <c r="F22" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6">
-      <c r="A23">
-        <v>20330051920055</v>
-      </c>
-      <c r="B23" t="s">
-        <v>70</v>
-      </c>
-      <c r="C23" t="s">
-        <v>68</v>
-      </c>
-      <c r="D23" t="s">
-        <v>100</v>
-      </c>
-      <c r="E23" t="s">
-        <v>10</v>
-      </c>
-      <c r="F23" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6">
-      <c r="A24">
-        <v>20330051920055</v>
-      </c>
-      <c r="B24" t="s">
-        <v>70</v>
-      </c>
-      <c r="C24" t="s">
-        <v>68</v>
-      </c>
-      <c r="D24" t="s">
-        <v>100</v>
-      </c>
-      <c r="E24" t="s">
-        <v>9</v>
-      </c>
-      <c r="F24" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6">
-      <c r="A25">
-        <v>20330051920097</v>
-      </c>
-      <c r="B25" t="s">
-        <v>71</v>
-      </c>
-      <c r="C25" t="s">
-        <v>87</v>
-      </c>
-      <c r="D25" t="s">
-        <v>101</v>
-      </c>
-      <c r="E25" t="s">
-        <v>6</v>
-      </c>
-      <c r="F25" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6">
-      <c r="A26">
-        <v>20330051920097</v>
-      </c>
-      <c r="B26" t="s">
-        <v>71</v>
-      </c>
-      <c r="C26" t="s">
-        <v>87</v>
-      </c>
-      <c r="D26" t="s">
-        <v>101</v>
-      </c>
-      <c r="E26" t="s">
-        <v>7</v>
-      </c>
-      <c r="F26" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6">
-      <c r="A27">
-        <v>20330051920097</v>
-      </c>
-      <c r="B27" t="s">
-        <v>71</v>
-      </c>
-      <c r="C27" t="s">
-        <v>87</v>
-      </c>
-      <c r="D27" t="s">
-        <v>101</v>
-      </c>
-      <c r="E27" t="s">
-        <v>10</v>
-      </c>
-      <c r="F27" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6">
-      <c r="A28">
-        <v>20330051920097</v>
-      </c>
-      <c r="B28" t="s">
-        <v>71</v>
-      </c>
-      <c r="C28" t="s">
-        <v>87</v>
-      </c>
-      <c r="D28" t="s">
-        <v>101</v>
-      </c>
-      <c r="E28" t="s">
-        <v>8</v>
-      </c>
-      <c r="F28" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6">
-      <c r="A29">
-        <v>20330051920099</v>
-      </c>
-      <c r="B29" t="s">
-        <v>72</v>
-      </c>
-      <c r="D29" t="s">
-        <v>102</v>
-      </c>
-      <c r="E29" t="s">
-        <v>6</v>
-      </c>
-      <c r="F29" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6">
-      <c r="A30">
-        <v>20330051920099</v>
-      </c>
-      <c r="B30" t="s">
-        <v>72</v>
-      </c>
-      <c r="D30" t="s">
-        <v>102</v>
-      </c>
-      <c r="E30" t="s">
-        <v>10</v>
-      </c>
-      <c r="F30" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6">
-      <c r="A31">
-        <v>20330051920099</v>
-      </c>
-      <c r="B31" t="s">
-        <v>72</v>
-      </c>
-      <c r="D31" t="s">
-        <v>102</v>
-      </c>
-      <c r="E31" t="s">
-        <v>9</v>
-      </c>
-      <c r="F31" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6">
-      <c r="A32">
-        <v>20330051920366</v>
-      </c>
-      <c r="B32" t="s">
-        <v>73</v>
-      </c>
-      <c r="C32" t="s">
-        <v>70</v>
-      </c>
-      <c r="D32" t="s">
-        <v>103</v>
-      </c>
-      <c r="E32" t="s">
-        <v>6</v>
-      </c>
-      <c r="F32" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6">
-      <c r="A33">
-        <v>20330051920366</v>
-      </c>
-      <c r="B33" t="s">
-        <v>73</v>
-      </c>
-      <c r="C33" t="s">
-        <v>70</v>
-      </c>
-      <c r="D33" t="s">
-        <v>103</v>
-      </c>
-      <c r="E33" t="s">
-        <v>7</v>
-      </c>
-      <c r="F33" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6">
-      <c r="A34">
-        <v>20330051920366</v>
-      </c>
-      <c r="B34" t="s">
-        <v>73</v>
-      </c>
-      <c r="C34" t="s">
-        <v>70</v>
-      </c>
-      <c r="D34" t="s">
-        <v>103</v>
-      </c>
-      <c r="E34" t="s">
-        <v>10</v>
-      </c>
-      <c r="F34" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6">
-      <c r="A35">
-        <v>20330051920366</v>
-      </c>
-      <c r="B35" t="s">
-        <v>73</v>
-      </c>
-      <c r="C35" t="s">
-        <v>70</v>
-      </c>
-      <c r="D35" t="s">
-        <v>103</v>
-      </c>
-      <c r="E35" t="s">
-        <v>8</v>
-      </c>
-      <c r="F35" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6">
-      <c r="A36">
-        <v>20330051920366</v>
-      </c>
-      <c r="B36" t="s">
-        <v>73</v>
-      </c>
-      <c r="C36" t="s">
-        <v>70</v>
-      </c>
-      <c r="D36" t="s">
-        <v>103</v>
-      </c>
-      <c r="E36" t="s">
-        <v>9</v>
-      </c>
-      <c r="F36" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6">
-      <c r="A37">
-        <v>20330051920367</v>
-      </c>
-      <c r="B37" t="s">
-        <v>73</v>
-      </c>
-      <c r="C37" t="s">
-        <v>70</v>
-      </c>
-      <c r="D37" t="s">
-        <v>104</v>
-      </c>
-      <c r="E37" t="s">
-        <v>6</v>
-      </c>
-      <c r="F37" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6">
-      <c r="A38">
-        <v>20330051920367</v>
-      </c>
-      <c r="B38" t="s">
-        <v>73</v>
-      </c>
-      <c r="C38" t="s">
-        <v>70</v>
-      </c>
-      <c r="D38" t="s">
-        <v>104</v>
-      </c>
-      <c r="E38" t="s">
-        <v>7</v>
-      </c>
-      <c r="F38" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6">
-      <c r="A39">
-        <v>20330051920367</v>
-      </c>
-      <c r="B39" t="s">
-        <v>73</v>
-      </c>
-      <c r="C39" t="s">
-        <v>70</v>
-      </c>
-      <c r="D39" t="s">
-        <v>104</v>
-      </c>
-      <c r="E39" t="s">
-        <v>10</v>
-      </c>
-      <c r="F39" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6">
-      <c r="A40">
-        <v>20330051920367</v>
-      </c>
-      <c r="B40" t="s">
-        <v>73</v>
-      </c>
-      <c r="C40" t="s">
-        <v>70</v>
-      </c>
-      <c r="D40" t="s">
-        <v>104</v>
-      </c>
-      <c r="E40" t="s">
-        <v>8</v>
-      </c>
-      <c r="F40" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6">
-      <c r="A41">
-        <v>20330051920367</v>
-      </c>
-      <c r="B41" t="s">
-        <v>73</v>
-      </c>
-      <c r="C41" t="s">
-        <v>70</v>
-      </c>
-      <c r="D41" t="s">
-        <v>104</v>
-      </c>
-      <c r="E41" t="s">
-        <v>9</v>
-      </c>
-      <c r="F41" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6">
-      <c r="A42">
-        <v>20330051920100</v>
-      </c>
-      <c r="B42" t="s">
-        <v>74</v>
-      </c>
-      <c r="C42" t="s">
-        <v>88</v>
-      </c>
-      <c r="D42" t="s">
-        <v>105</v>
-      </c>
-      <c r="E42" t="s">
-        <v>6</v>
-      </c>
-      <c r="F42" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6">
-      <c r="A43">
-        <v>20330051920100</v>
-      </c>
-      <c r="B43" t="s">
-        <v>74</v>
-      </c>
-      <c r="C43" t="s">
-        <v>88</v>
-      </c>
-      <c r="D43" t="s">
-        <v>105</v>
-      </c>
-      <c r="E43" t="s">
-        <v>7</v>
-      </c>
-      <c r="F43" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6">
-      <c r="A44">
-        <v>20330051920100</v>
-      </c>
-      <c r="B44" t="s">
-        <v>74</v>
-      </c>
-      <c r="C44" t="s">
-        <v>88</v>
-      </c>
-      <c r="D44" t="s">
-        <v>105</v>
-      </c>
-      <c r="E44" t="s">
-        <v>10</v>
-      </c>
-      <c r="F44" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6">
-      <c r="A45">
-        <v>20330051920100</v>
-      </c>
-      <c r="B45" t="s">
-        <v>74</v>
-      </c>
-      <c r="C45" t="s">
-        <v>88</v>
-      </c>
-      <c r="D45" t="s">
-        <v>105</v>
-      </c>
-      <c r="E45" t="s">
-        <v>9</v>
-      </c>
-      <c r="F45" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6">
-      <c r="A46">
-        <v>20330051920107</v>
-      </c>
-      <c r="B46" t="s">
-        <v>75</v>
-      </c>
-      <c r="C46" t="s">
-        <v>75</v>
-      </c>
-      <c r="D46" t="s">
-        <v>106</v>
-      </c>
-      <c r="E46" t="s">
-        <v>6</v>
-      </c>
-      <c r="F46" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6">
-      <c r="A47">
-        <v>20330051920107</v>
-      </c>
-      <c r="B47" t="s">
-        <v>75</v>
-      </c>
-      <c r="C47" t="s">
-        <v>75</v>
-      </c>
-      <c r="D47" t="s">
-        <v>106</v>
-      </c>
-      <c r="E47" t="s">
-        <v>7</v>
-      </c>
-      <c r="F47" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6">
-      <c r="A48">
-        <v>20330051920107</v>
-      </c>
-      <c r="B48" t="s">
-        <v>75</v>
-      </c>
-      <c r="C48" t="s">
-        <v>75</v>
-      </c>
-      <c r="D48" t="s">
-        <v>106</v>
-      </c>
-      <c r="E48" t="s">
-        <v>10</v>
-      </c>
-      <c r="F48" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6">
-      <c r="A49">
-        <v>20330051920109</v>
-      </c>
-      <c r="B49" t="s">
-        <v>76</v>
-      </c>
-      <c r="C49" t="s">
-        <v>83</v>
-      </c>
-      <c r="D49" t="s">
-        <v>107</v>
-      </c>
-      <c r="E49" t="s">
-        <v>6</v>
-      </c>
-      <c r="F49" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6">
-      <c r="A50">
-        <v>20330051920109</v>
-      </c>
-      <c r="B50" t="s">
-        <v>76</v>
-      </c>
-      <c r="C50" t="s">
-        <v>83</v>
-      </c>
-      <c r="D50" t="s">
-        <v>107</v>
-      </c>
-      <c r="E50" t="s">
-        <v>7</v>
-      </c>
-      <c r="F50" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6">
-      <c r="A51">
-        <v>20330051920109</v>
-      </c>
-      <c r="B51" t="s">
-        <v>76</v>
-      </c>
-      <c r="C51" t="s">
-        <v>83</v>
-      </c>
-      <c r="D51" t="s">
-        <v>107</v>
-      </c>
-      <c r="E51" t="s">
-        <v>9</v>
-      </c>
-      <c r="F51" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6">
-      <c r="A52">
-        <v>20330051920111</v>
-      </c>
-      <c r="B52" t="s">
-        <v>77</v>
-      </c>
-      <c r="C52" t="s">
-        <v>89</v>
-      </c>
-      <c r="D52" t="s">
-        <v>108</v>
-      </c>
-      <c r="E52" t="s">
-        <v>6</v>
-      </c>
-      <c r="F52" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6">
-      <c r="A53">
-        <v>20330051920112</v>
-      </c>
-      <c r="B53" t="s">
-        <v>78</v>
-      </c>
-      <c r="C53" t="s">
-        <v>90</v>
-      </c>
-      <c r="D53" t="s">
-        <v>109</v>
-      </c>
-      <c r="E53" t="s">
-        <v>9</v>
-      </c>
-      <c r="F53" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6">
-      <c r="A54">
-        <v>20330051920113</v>
-      </c>
-      <c r="B54" t="s">
-        <v>79</v>
-      </c>
-      <c r="C54" t="s">
-        <v>91</v>
-      </c>
-      <c r="D54" t="s">
-        <v>110</v>
-      </c>
-      <c r="E54" t="s">
-        <v>10</v>
-      </c>
-      <c r="F54" t="s">
-        <v>54</v>
       </c>
     </row>
   </sheetData>
@@ -4678,336 +3724,336 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2">
-        <v>20330051920366</v>
+        <v>20330051920097</v>
       </c>
       <c r="B2" t="s">
-        <v>73</v>
+        <v>62</v>
       </c>
       <c r="C2" t="s">
+        <v>67</v>
+      </c>
+      <c r="D2" t="s">
         <v>70</v>
       </c>
-      <c r="D2" t="s">
-        <v>103</v>
-      </c>
       <c r="E2">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3">
-        <v>20330051920367</v>
+        <v>20330051920099</v>
       </c>
       <c r="B3" t="s">
-        <v>73</v>
-      </c>
-      <c r="C3" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="D3" t="s">
-        <v>104</v>
+        <v>71</v>
       </c>
       <c r="E3">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>20330051920050</v>
+        <v>20330051920100</v>
       </c>
       <c r="B4" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="D4" t="s">
-        <v>96</v>
+        <v>72</v>
       </c>
       <c r="E4">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>20330051920365</v>
+        <v>20330051920107</v>
       </c>
       <c r="B5" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C5" t="s">
-        <v>84</v>
+        <v>65</v>
       </c>
       <c r="D5" t="s">
-        <v>97</v>
+        <v>73</v>
       </c>
       <c r="E5">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>20330051920052</v>
+        <v>20330051920113</v>
       </c>
       <c r="B6" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C6" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="D6" t="s">
-        <v>98</v>
+        <v>74</v>
       </c>
       <c r="E6">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>20330051920055</v>
+        <v>20330051920039</v>
       </c>
       <c r="B7" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="C7" t="s">
-        <v>68</v>
+        <v>100</v>
       </c>
       <c r="D7" t="s">
-        <v>100</v>
+        <v>118</v>
       </c>
       <c r="E7">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>20330051920097</v>
+        <v>20330051920040</v>
       </c>
       <c r="B8" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="C8" t="s">
-        <v>87</v>
+        <v>101</v>
       </c>
       <c r="D8" t="s">
-        <v>101</v>
+        <v>119</v>
       </c>
       <c r="E8">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>20330051920100</v>
+        <v>20330051920042</v>
       </c>
       <c r="B9" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="C9" t="s">
-        <v>88</v>
+        <v>102</v>
       </c>
       <c r="D9" t="s">
-        <v>105</v>
+        <v>120</v>
       </c>
       <c r="E9">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>20330051920099</v>
+        <v>20330051920043</v>
       </c>
       <c r="B10" t="s">
-        <v>72</v>
+        <v>78</v>
+      </c>
+      <c r="C10" t="s">
+        <v>103</v>
       </c>
       <c r="D10" t="s">
-        <v>102</v>
+        <v>121</v>
       </c>
       <c r="E10">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>20330051920107</v>
+        <v>20330051920044</v>
       </c>
       <c r="B11" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="C11" t="s">
-        <v>75</v>
+        <v>104</v>
       </c>
       <c r="D11" t="s">
-        <v>106</v>
+        <v>122</v>
       </c>
       <c r="E11">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>20330051920109</v>
+        <v>20330051920045</v>
       </c>
       <c r="B12" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="C12" t="s">
-        <v>83</v>
+        <v>105</v>
       </c>
       <c r="D12" t="s">
-        <v>107</v>
+        <v>123</v>
       </c>
       <c r="E12">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>20330051920039</v>
+        <v>20330051920046</v>
       </c>
       <c r="B13" t="s">
-        <v>62</v>
+        <v>81</v>
       </c>
       <c r="C13" t="s">
-        <v>80</v>
+        <v>106</v>
       </c>
       <c r="D13" t="s">
-        <v>92</v>
+        <v>124</v>
       </c>
       <c r="E13">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>20330051920042</v>
+        <v>20330051920048</v>
       </c>
       <c r="B14" t="s">
-        <v>64</v>
+        <v>82</v>
       </c>
       <c r="C14" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="D14" t="s">
-        <v>94</v>
+        <v>125</v>
       </c>
       <c r="E14">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>20330051920040</v>
+        <v>20330051920050</v>
       </c>
       <c r="B15" t="s">
-        <v>63</v>
+        <v>83</v>
       </c>
       <c r="C15" t="s">
-        <v>81</v>
+        <v>62</v>
       </c>
       <c r="D15" t="s">
-        <v>93</v>
+        <v>126</v>
       </c>
       <c r="E15">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>20330051920046</v>
+        <v>20330051920051</v>
       </c>
       <c r="B16" t="s">
-        <v>65</v>
+        <v>84</v>
       </c>
       <c r="C16" t="s">
-        <v>83</v>
+        <v>107</v>
       </c>
       <c r="D16" t="s">
-        <v>95</v>
+        <v>124</v>
       </c>
       <c r="E16">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>20330051920053</v>
+        <v>20330051920365</v>
       </c>
       <c r="B17" t="s">
-        <v>69</v>
+        <v>85</v>
       </c>
       <c r="C17" t="s">
-        <v>86</v>
+        <v>108</v>
       </c>
       <c r="D17" t="s">
-        <v>99</v>
+        <v>127</v>
       </c>
       <c r="E17">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>20330051920111</v>
+        <v>20330051920052</v>
       </c>
       <c r="B18" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="C18" t="s">
-        <v>89</v>
+        <v>109</v>
       </c>
       <c r="D18" t="s">
-        <v>108</v>
+        <v>128</v>
       </c>
       <c r="E18">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>20330051920112</v>
+        <v>20330051920053</v>
       </c>
       <c r="B19" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="C19" t="s">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="D19" t="s">
-        <v>109</v>
+        <v>129</v>
       </c>
       <c r="E19">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>20330051920113</v>
+        <v>20330051920055</v>
       </c>
       <c r="B20" t="s">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="C20" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="D20" t="s">
-        <v>110</v>
+        <v>130</v>
       </c>
       <c r="E20">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21">
-        <v>20330051920043</v>
+        <v>20330051920056</v>
       </c>
       <c r="B21" t="s">
+        <v>89</v>
+      </c>
+      <c r="C21" t="s">
         <v>111</v>
       </c>
-      <c r="C21" t="s">
-        <v>123</v>
-      </c>
       <c r="D21" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E21">
         <v>0</v>
@@ -5015,16 +4061,16 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22">
-        <v>20330051920044</v>
+        <v>20330051920057</v>
       </c>
       <c r="B22" t="s">
+        <v>88</v>
+      </c>
+      <c r="C22" t="s">
         <v>112</v>
       </c>
-      <c r="C22" t="s">
-        <v>124</v>
-      </c>
       <c r="D22" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E22">
         <v>0</v>
@@ -5032,16 +4078,16 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23">
-        <v>20330051920045</v>
+        <v>20330051920095</v>
       </c>
       <c r="B23" t="s">
-        <v>113</v>
+        <v>90</v>
       </c>
       <c r="C23" t="s">
-        <v>125</v>
+        <v>89</v>
       </c>
       <c r="D23" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E23">
         <v>0</v>
@@ -5049,16 +4095,16 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24">
-        <v>20330051920048</v>
+        <v>20330051920096</v>
       </c>
       <c r="B24" t="s">
-        <v>114</v>
+        <v>91</v>
       </c>
       <c r="C24" t="s">
-        <v>70</v>
+        <v>113</v>
       </c>
       <c r="D24" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E24">
         <v>0</v>
@@ -5066,16 +4112,16 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25">
-        <v>20330051920051</v>
+        <v>20330051920366</v>
       </c>
       <c r="B25" t="s">
-        <v>115</v>
+        <v>92</v>
       </c>
       <c r="C25" t="s">
-        <v>126</v>
+        <v>88</v>
       </c>
       <c r="D25" t="s">
-        <v>95</v>
+        <v>135</v>
       </c>
       <c r="E25">
         <v>0</v>
@@ -5083,13 +4129,13 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26">
-        <v>20330051920056</v>
+        <v>20330051920367</v>
       </c>
       <c r="B26" t="s">
-        <v>116</v>
+        <v>92</v>
       </c>
       <c r="C26" t="s">
-        <v>127</v>
+        <v>88</v>
       </c>
       <c r="D26" t="s">
         <v>136</v>
@@ -5100,13 +4146,13 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27">
-        <v>20330051920057</v>
+        <v>20330051920101</v>
       </c>
       <c r="B27" t="s">
-        <v>70</v>
+        <v>93</v>
       </c>
       <c r="C27" t="s">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="D27" t="s">
         <v>137</v>
@@ -5117,13 +4163,13 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28">
-        <v>20330051920095</v>
+        <v>20330051920102</v>
       </c>
       <c r="B28" t="s">
-        <v>117</v>
+        <v>94</v>
       </c>
       <c r="C28" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D28" t="s">
         <v>138</v>
@@ -5134,13 +4180,13 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29">
-        <v>20330051920096</v>
+        <v>20330051920104</v>
       </c>
       <c r="B29" t="s">
-        <v>118</v>
+        <v>95</v>
       </c>
       <c r="C29" t="s">
-        <v>129</v>
+        <v>110</v>
       </c>
       <c r="D29" t="s">
         <v>139</v>
@@ -5151,13 +4197,13 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30">
-        <v>20330051920101</v>
+        <v>20330051920105</v>
       </c>
       <c r="B30" t="s">
-        <v>119</v>
+        <v>96</v>
       </c>
       <c r="C30" t="s">
-        <v>130</v>
+        <v>91</v>
       </c>
       <c r="D30" t="s">
         <v>140</v>
@@ -5168,13 +4214,13 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31">
-        <v>20330051920102</v>
+        <v>20330051920109</v>
       </c>
       <c r="B31" t="s">
-        <v>120</v>
+        <v>97</v>
       </c>
       <c r="C31" t="s">
-        <v>131</v>
+        <v>106</v>
       </c>
       <c r="D31" t="s">
         <v>141</v>
@@ -5185,13 +4231,13 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32">
-        <v>20330051920104</v>
+        <v>20330051920111</v>
       </c>
       <c r="B32" t="s">
-        <v>121</v>
+        <v>98</v>
       </c>
       <c r="C32" t="s">
-        <v>86</v>
+        <v>116</v>
       </c>
       <c r="D32" t="s">
         <v>142</v>
@@ -5202,13 +4248,13 @@
     </row>
     <row r="33" spans="1:5">
       <c r="A33">
-        <v>20330051920105</v>
+        <v>20330051920112</v>
       </c>
       <c r="B33" t="s">
-        <v>122</v>
+        <v>99</v>
       </c>
       <c r="C33" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D33" t="s">
         <v>143</v>
@@ -5224,7 +4270,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5256,22 +4302,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>20330051920040</v>
+        <v>20330051920039</v>
       </c>
       <c r="B2" t="s">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="C2" t="s">
-        <v>81</v>
+        <v>100</v>
       </c>
       <c r="D2" t="s">
-        <v>93</v>
+        <v>118</v>
       </c>
       <c r="E2" t="s">
         <v>5</v>
       </c>
       <c r="F2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -5279,39 +4325,39 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>20330051920040</v>
+        <v>20330051920039</v>
       </c>
       <c r="B3" t="s">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="C3" t="s">
-        <v>81</v>
+        <v>100</v>
       </c>
       <c r="D3" t="s">
-        <v>93</v>
+        <v>118</v>
       </c>
       <c r="E3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G3">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920042</v>
+        <v>20330051920050</v>
       </c>
       <c r="B4" t="s">
-        <v>64</v>
+        <v>83</v>
       </c>
       <c r="C4" t="s">
-        <v>82</v>
+        <v>62</v>
       </c>
       <c r="D4" t="s">
-        <v>94</v>
+        <v>126</v>
       </c>
       <c r="E4" t="s">
         <v>6</v>
@@ -5320,44 +4366,44 @@
         <v>52</v>
       </c>
       <c r="G4">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920042</v>
+        <v>20330051920050</v>
       </c>
       <c r="B5" t="s">
-        <v>64</v>
+        <v>83</v>
       </c>
       <c r="C5" t="s">
-        <v>82</v>
+        <v>62</v>
       </c>
       <c r="D5" t="s">
-        <v>94</v>
+        <v>126</v>
       </c>
       <c r="E5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F5" t="s">
         <v>54</v>
       </c>
       <c r="G5">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>20330051920046</v>
+        <v>20330051920100</v>
       </c>
       <c r="B6" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C6" t="s">
-        <v>83</v>
+        <v>68</v>
       </c>
       <c r="D6" t="s">
-        <v>95</v>
+        <v>72</v>
       </c>
       <c r="E6" t="s">
         <v>6</v>
@@ -5366,24 +4412,24 @@
         <v>52</v>
       </c>
       <c r="G6">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>20330051920053</v>
+        <v>20330051920100</v>
       </c>
       <c r="B7" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="C7" t="s">
-        <v>86</v>
+        <v>68</v>
       </c>
       <c r="D7" t="s">
-        <v>99</v>
+        <v>72</v>
       </c>
       <c r="E7" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F7" t="s">
         <v>53</v>
@@ -5394,16 +4440,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>20330051920111</v>
+        <v>20330051920042</v>
       </c>
       <c r="B8" t="s">
         <v>77</v>
       </c>
       <c r="C8" t="s">
-        <v>89</v>
+        <v>102</v>
       </c>
       <c r="D8" t="s">
-        <v>108</v>
+        <v>120</v>
       </c>
       <c r="E8" t="s">
         <v>6</v>
@@ -5412,52 +4458,118 @@
         <v>52</v>
       </c>
       <c r="G8">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>20330051920112</v>
+        <v>20330051920046</v>
       </c>
       <c r="B9" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="C9" t="s">
-        <v>90</v>
+        <v>106</v>
       </c>
       <c r="D9" t="s">
-        <v>109</v>
+        <v>124</v>
       </c>
       <c r="E9" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F9" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="G9">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
+        <v>20330051920052</v>
+      </c>
+      <c r="B10" t="s">
+        <v>86</v>
+      </c>
+      <c r="C10" t="s">
+        <v>109</v>
+      </c>
+      <c r="D10" t="s">
+        <v>128</v>
+      </c>
+      <c r="E10" t="s">
+        <v>6</v>
+      </c>
+      <c r="F10" t="s">
+        <v>52</v>
+      </c>
+      <c r="G10">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11">
+        <v>20330051920099</v>
+      </c>
+      <c r="B11" t="s">
+        <v>63</v>
+      </c>
+      <c r="D11" t="s">
+        <v>71</v>
+      </c>
+      <c r="E11" t="s">
+        <v>10</v>
+      </c>
+      <c r="F11" t="s">
+        <v>53</v>
+      </c>
+      <c r="G11">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12">
+        <v>20330051920107</v>
+      </c>
+      <c r="B12" t="s">
+        <v>65</v>
+      </c>
+      <c r="C12" t="s">
+        <v>65</v>
+      </c>
+      <c r="D12" t="s">
+        <v>73</v>
+      </c>
+      <c r="E12" t="s">
+        <v>10</v>
+      </c>
+      <c r="F12" t="s">
+        <v>53</v>
+      </c>
+      <c r="G12">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13">
         <v>20330051920113</v>
       </c>
-      <c r="B10" t="s">
-        <v>79</v>
-      </c>
-      <c r="C10" t="s">
-        <v>91</v>
-      </c>
-      <c r="D10" t="s">
-        <v>110</v>
-      </c>
-      <c r="E10" t="s">
-        <v>10</v>
-      </c>
-      <c r="F10" t="s">
-        <v>54</v>
-      </c>
-      <c r="G10">
+      <c r="B13" t="s">
+        <v>66</v>
+      </c>
+      <c r="C13" t="s">
+        <v>69</v>
+      </c>
+      <c r="D13" t="s">
+        <v>74</v>
+      </c>
+      <c r="E13" t="s">
+        <v>10</v>
+      </c>
+      <c r="F13" t="s">
+        <v>53</v>
+      </c>
+      <c r="G13">
         <v>-1</v>
       </c>
     </row>

--- a/grupos/3BEM - Estadisticos 20211.xlsx
+++ b/grupos/3BEM - Estadisticos 20211.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="279" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="144">
   <si>
     <t>Materia</t>
   </si>
@@ -179,18 +179,18 @@
     <t>Rodríguez Román Leticia</t>
   </si>
   <si>
+    <t>Cruz Alejo José Armando</t>
+  </si>
+  <si>
+    <t>Avila Coronado Julieta</t>
+  </si>
+  <si>
+    <t>Camarillo Aburto Raymundo</t>
+  </si>
+  <si>
     <t>Molina Quezada Raúl</t>
   </si>
   <si>
-    <t>Cruz Alejo José Armando</t>
-  </si>
-  <si>
-    <t>Avila Coronado Julieta</t>
-  </si>
-  <si>
-    <t>Camarillo Aburto Raymundo</t>
-  </si>
-  <si>
     <t>Aurioles Maldonado Luis Gustavo</t>
   </si>
   <si>
@@ -206,223 +206,223 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>NUBE</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>XOTLANIHUA</t>
+  </si>
+  <si>
+    <t>ALEMAN</t>
+  </si>
+  <si>
+    <t>TEXCAHUA</t>
+  </si>
+  <si>
+    <t>CHRISTIAN YAIR</t>
+  </si>
+  <si>
+    <t>ROSA ISELA</t>
+  </si>
+  <si>
+    <t>ALEXANDER</t>
+  </si>
+  <si>
+    <t>ALVAREZ</t>
+  </si>
+  <si>
+    <t>AMADOR</t>
+  </si>
+  <si>
+    <t>ANASTACIO</t>
+  </si>
+  <si>
+    <t>AGUILAR</t>
+  </si>
+  <si>
+    <t>BERNARDO</t>
+  </si>
+  <si>
+    <t>CITALAN</t>
+  </si>
+  <si>
+    <t>CID</t>
+  </si>
+  <si>
+    <t>COLOHUA</t>
+  </si>
+  <si>
+    <t>DE LA CRUZ</t>
+  </si>
+  <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>DIAZ</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>GOMEZ</t>
+  </si>
+  <si>
+    <t>GUEVARA</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
     <t>DE JESUS</t>
   </si>
   <si>
     <t>MENDIZABAL</t>
   </si>
   <si>
-    <t>NUBE</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>XOTLANIHUA</t>
+    <t>NAJERA</t>
+  </si>
+  <si>
+    <t>ORTIZ</t>
+  </si>
+  <si>
+    <t>OLMOS</t>
+  </si>
+  <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>TELLEZ</t>
+  </si>
+  <si>
+    <t>VALENTE</t>
+  </si>
+  <si>
+    <t>VASQUEZ</t>
+  </si>
+  <si>
+    <t>CONCHE</t>
+  </si>
+  <si>
+    <t>PORRAS</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>GARCÍA</t>
+  </si>
+  <si>
+    <t>CONCHOA</t>
+  </si>
+  <si>
+    <t>ROMANOS</t>
+  </si>
+  <si>
+    <t>VALENCIA</t>
+  </si>
+  <si>
+    <t>MARROQUIN</t>
+  </si>
+  <si>
+    <t>VAZQUEZ</t>
+  </si>
+  <si>
+    <t>SEGURA</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>HERRERA</t>
+  </si>
+  <si>
+    <t>VELAZQUEZ</t>
+  </si>
+  <si>
+    <t>MARCELINO</t>
   </si>
   <si>
     <t>EVARISTO</t>
   </si>
   <si>
-    <t>ALEMAN</t>
-  </si>
-  <si>
-    <t>TEXCAHUA</t>
+    <t>ROSETE</t>
+  </si>
+  <si>
+    <t>ROBLES</t>
+  </si>
+  <si>
+    <t>GAMEZ</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>GUSTAVO</t>
+  </si>
+  <si>
+    <t>FRANCISCO ALAN</t>
+  </si>
+  <si>
+    <t>HIRAM FABIAN</t>
+  </si>
+  <si>
+    <t>RAUL</t>
+  </si>
+  <si>
+    <t>URIEL</t>
+  </si>
+  <si>
+    <t>MISAEL</t>
+  </si>
+  <si>
+    <t>JESUS</t>
+  </si>
+  <si>
+    <t>DAVID</t>
+  </si>
+  <si>
+    <t>YAHIR</t>
+  </si>
+  <si>
+    <t>BRUNO AZAEL</t>
+  </si>
+  <si>
+    <t>CESAR</t>
+  </si>
+  <si>
+    <t>MARIA ASUNCION</t>
+  </si>
+  <si>
+    <t>MARCO ANTONIO</t>
+  </si>
+  <si>
+    <t>ROBERTO</t>
+  </si>
+  <si>
+    <t>NOEL ALBERTO</t>
+  </si>
+  <si>
+    <t>LUIS ALBERTO</t>
+  </si>
+  <si>
+    <t>ADRIAN</t>
   </si>
   <si>
     <t>ALDAIR ALAN</t>
   </si>
   <si>
     <t>ALDER ALBERTO</t>
-  </si>
-  <si>
-    <t>CHRISTIAN YAIR</t>
-  </si>
-  <si>
-    <t>ROSA ISELA</t>
-  </si>
-  <si>
-    <t>ALEXANDER</t>
-  </si>
-  <si>
-    <t>ALVAREZ</t>
-  </si>
-  <si>
-    <t>AMADOR</t>
-  </si>
-  <si>
-    <t>ANASTACIO</t>
-  </si>
-  <si>
-    <t>AGUILAR</t>
-  </si>
-  <si>
-    <t>BERNARDO</t>
-  </si>
-  <si>
-    <t>CITALAN</t>
-  </si>
-  <si>
-    <t>CID</t>
-  </si>
-  <si>
-    <t>COLOHUA</t>
-  </si>
-  <si>
-    <t>DE LA CRUZ</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>DIAZ</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>GOMEZ</t>
-  </si>
-  <si>
-    <t>GUEVARA</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>NAJERA</t>
-  </si>
-  <si>
-    <t>ORTIZ</t>
-  </si>
-  <si>
-    <t>OLMOS</t>
-  </si>
-  <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>TELLEZ</t>
-  </si>
-  <si>
-    <t>VALENTE</t>
-  </si>
-  <si>
-    <t>VASQUEZ</t>
-  </si>
-  <si>
-    <t>CONCHE</t>
-  </si>
-  <si>
-    <t>PORRAS</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>GARCÍA</t>
-  </si>
-  <si>
-    <t>CONCHOA</t>
-  </si>
-  <si>
-    <t>ROMANOS</t>
-  </si>
-  <si>
-    <t>VALENCIA</t>
-  </si>
-  <si>
-    <t>MARROQUIN</t>
-  </si>
-  <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
-    <t>SEGURA</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>HERRERA</t>
-  </si>
-  <si>
-    <t>VELAZQUEZ</t>
-  </si>
-  <si>
-    <t>MARCELINO</t>
-  </si>
-  <si>
-    <t>ROSETE</t>
-  </si>
-  <si>
-    <t>ROBLES</t>
-  </si>
-  <si>
-    <t>GAMEZ</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>GUSTAVO</t>
-  </si>
-  <si>
-    <t>FRANCISCO ALAN</t>
-  </si>
-  <si>
-    <t>HIRAM FABIAN</t>
-  </si>
-  <si>
-    <t>RAUL</t>
-  </si>
-  <si>
-    <t>URIEL</t>
-  </si>
-  <si>
-    <t>MISAEL</t>
-  </si>
-  <si>
-    <t>JESUS</t>
-  </si>
-  <si>
-    <t>DAVID</t>
-  </si>
-  <si>
-    <t>YAHIR</t>
-  </si>
-  <si>
-    <t>BRUNO AZAEL</t>
-  </si>
-  <si>
-    <t>CESAR</t>
-  </si>
-  <si>
-    <t>MARIA ASUNCION</t>
-  </si>
-  <si>
-    <t>MARCO ANTONIO</t>
-  </si>
-  <si>
-    <t>ROBERTO</t>
-  </si>
-  <si>
-    <t>NOEL ALBERTO</t>
-  </si>
-  <si>
-    <t>LUIS ALBERTO</t>
-  </si>
-  <si>
-    <t>ADRIAN</t>
   </si>
   <si>
     <t>ELI ANTONIO</t>
@@ -1353,7 +1353,7 @@
         <v>10</v>
       </c>
       <c r="M9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N9">
         <v>-1</v>
@@ -1389,7 +1389,7 @@
         <v>10</v>
       </c>
       <c r="Y9">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10" spans="1:25">
@@ -1643,7 +1643,7 @@
         <v>10</v>
       </c>
       <c r="G13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="H13">
         <v>6</v>
@@ -1661,7 +1661,7 @@
         <v>10</v>
       </c>
       <c r="M13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N13">
         <v>-1</v>
@@ -1697,7 +1697,7 @@
         <v>10</v>
       </c>
       <c r="Y13">
-        <v>-1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="14" spans="1:25">
@@ -3402,7 +3402,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B3" t="s">
         <v>53</v>
@@ -3414,27 +3414,27 @@
         <v>27</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F3">
         <v>84.38</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>15.63</v>
       </c>
       <c r="H3">
-        <v>9.5</v>
+        <v>7.7</v>
       </c>
       <c r="I3">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J3">
-        <v>15.63</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B4" t="s">
         <v>54</v>
@@ -3443,19 +3443,19 @@
         <v>32</v>
       </c>
       <c r="D4">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E4">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F4">
-        <v>84.38</v>
+        <v>87.5</v>
       </c>
       <c r="G4">
-        <v>15.63</v>
+        <v>12.5</v>
       </c>
       <c r="H4">
-        <v>7.7</v>
+        <v>8</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -3466,7 +3466,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B5" t="s">
         <v>55</v>
@@ -3487,7 +3487,7 @@
         <v>12.5</v>
       </c>
       <c r="H5">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -3498,7 +3498,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="B6" t="s">
         <v>56</v>
@@ -3507,25 +3507,25 @@
         <v>32</v>
       </c>
       <c r="D6">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E6">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F6">
-        <v>87.5</v>
+        <v>90.63</v>
       </c>
       <c r="G6">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="H6">
-        <v>7.8</v>
+        <v>9.4</v>
       </c>
       <c r="I6">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J6">
-        <v>0</v>
+        <v>9.380000000000001</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -3567,7 +3567,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -3596,99 +3596,62 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2">
-        <v>20330051920097</v>
+        <v>20330051920100</v>
       </c>
       <c r="B2" t="s">
         <v>62</v>
       </c>
       <c r="C2" t="s">
+        <v>65</v>
+      </c>
+      <c r="D2" t="s">
         <v>67</v>
       </c>
-      <c r="D2" t="s">
-        <v>70</v>
-      </c>
       <c r="E2" t="s">
         <v>10</v>
       </c>
       <c r="F2" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
     </row>
     <row r="3" spans="1:6">
       <c r="A3">
-        <v>20330051920099</v>
+        <v>20330051920107</v>
       </c>
       <c r="B3" t="s">
         <v>63</v>
       </c>
+      <c r="C3" t="s">
+        <v>63</v>
+      </c>
       <c r="D3" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="E3" t="s">
         <v>10</v>
       </c>
       <c r="F3" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4">
-        <v>20330051920100</v>
+        <v>20330051920113</v>
       </c>
       <c r="B4" t="s">
         <v>64</v>
       </c>
       <c r="C4" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="D4" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="E4" t="s">
         <v>10</v>
       </c>
       <c r="F4" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5">
-        <v>20330051920107</v>
-      </c>
-      <c r="B5" t="s">
-        <v>65</v>
-      </c>
-      <c r="C5" t="s">
-        <v>65</v>
-      </c>
-      <c r="D5" t="s">
-        <v>73</v>
-      </c>
-      <c r="E5" t="s">
-        <v>10</v>
-      </c>
-      <c r="F5" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6">
-        <v>20330051920113</v>
-      </c>
-      <c r="B6" t="s">
-        <v>66</v>
-      </c>
-      <c r="C6" t="s">
-        <v>69</v>
-      </c>
-      <c r="D6" t="s">
-        <v>74</v>
-      </c>
-      <c r="E6" t="s">
-        <v>10</v>
-      </c>
-      <c r="F6" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
     </row>
   </sheetData>
@@ -3724,16 +3687,16 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2">
-        <v>20330051920097</v>
+        <v>20330051920100</v>
       </c>
       <c r="B2" t="s">
         <v>62</v>
       </c>
       <c r="C2" t="s">
+        <v>65</v>
+      </c>
+      <c r="D2" t="s">
         <v>67</v>
-      </c>
-      <c r="D2" t="s">
-        <v>70</v>
       </c>
       <c r="E2">
         <v>1</v>
@@ -3741,13 +3704,16 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3">
-        <v>20330051920099</v>
+        <v>20330051920107</v>
       </c>
       <c r="B3" t="s">
         <v>63</v>
       </c>
+      <c r="C3" t="s">
+        <v>63</v>
+      </c>
       <c r="D3" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="E3">
         <v>1</v>
@@ -3755,16 +3721,16 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>20330051920100</v>
+        <v>20330051920113</v>
       </c>
       <c r="B4" t="s">
         <v>64</v>
       </c>
       <c r="C4" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="D4" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="E4">
         <v>1</v>
@@ -3772,47 +3738,47 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>20330051920107</v>
+        <v>20330051920039</v>
       </c>
       <c r="B5" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="C5" t="s">
-        <v>65</v>
+        <v>97</v>
       </c>
       <c r="D5" t="s">
-        <v>73</v>
+        <v>116</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>20330051920113</v>
+        <v>20330051920040</v>
       </c>
       <c r="B6" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="C6" t="s">
-        <v>69</v>
+        <v>98</v>
       </c>
       <c r="D6" t="s">
-        <v>74</v>
+        <v>117</v>
       </c>
       <c r="E6">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>20330051920039</v>
+        <v>20330051920042</v>
       </c>
       <c r="B7" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="C7" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D7" t="s">
         <v>118</v>
@@ -3823,13 +3789,13 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>20330051920040</v>
+        <v>20330051920043</v>
       </c>
       <c r="B8" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="C8" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D8" t="s">
         <v>119</v>
@@ -3840,13 +3806,13 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>20330051920042</v>
+        <v>20330051920044</v>
       </c>
       <c r="B9" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="C9" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D9" t="s">
         <v>120</v>
@@ -3857,13 +3823,13 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>20330051920043</v>
+        <v>20330051920045</v>
       </c>
       <c r="B10" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="C10" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D10" t="s">
         <v>121</v>
@@ -3874,13 +3840,13 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>20330051920044</v>
+        <v>20330051920046</v>
       </c>
       <c r="B11" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="C11" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D11" t="s">
         <v>122</v>
@@ -3891,13 +3857,13 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>20330051920045</v>
+        <v>20330051920048</v>
       </c>
       <c r="B12" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="C12" t="s">
-        <v>105</v>
+        <v>83</v>
       </c>
       <c r="D12" t="s">
         <v>123</v>
@@ -3908,13 +3874,13 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>20330051920046</v>
+        <v>20330051920050</v>
       </c>
       <c r="B13" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="C13" t="s">
-        <v>106</v>
+        <v>87</v>
       </c>
       <c r="D13" t="s">
         <v>124</v>
@@ -3925,16 +3891,16 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>20330051920048</v>
+        <v>20330051920051</v>
       </c>
       <c r="B14" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="C14" t="s">
-        <v>88</v>
+        <v>104</v>
       </c>
       <c r="D14" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="E14">
         <v>0</v>
@@ -3942,16 +3908,16 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>20330051920050</v>
+        <v>20330051920365</v>
       </c>
       <c r="B15" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="C15" t="s">
-        <v>62</v>
+        <v>105</v>
       </c>
       <c r="D15" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E15">
         <v>0</v>
@@ -3959,16 +3925,16 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>20330051920051</v>
+        <v>20330051920052</v>
       </c>
       <c r="B16" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="C16" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D16" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E16">
         <v>0</v>
@@ -3976,13 +3942,13 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>20330051920365</v>
+        <v>20330051920053</v>
       </c>
       <c r="B17" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="C17" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D17" t="s">
         <v>127</v>
@@ -3993,13 +3959,13 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>20330051920052</v>
+        <v>20330051920055</v>
       </c>
       <c r="B18" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="C18" t="s">
-        <v>109</v>
+        <v>81</v>
       </c>
       <c r="D18" t="s">
         <v>128</v>
@@ -4010,13 +3976,13 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>20330051920053</v>
+        <v>20330051920056</v>
       </c>
       <c r="B19" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="C19" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="D19" t="s">
         <v>129</v>
@@ -4027,13 +3993,13 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>20330051920055</v>
+        <v>20330051920057</v>
       </c>
       <c r="B20" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="C20" t="s">
-        <v>86</v>
+        <v>109</v>
       </c>
       <c r="D20" t="s">
         <v>130</v>
@@ -4044,13 +4010,13 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21">
-        <v>20330051920056</v>
+        <v>20330051920095</v>
       </c>
       <c r="B21" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="C21" t="s">
-        <v>111</v>
+        <v>84</v>
       </c>
       <c r="D21" t="s">
         <v>131</v>
@@ -4061,13 +4027,13 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22">
-        <v>20330051920057</v>
+        <v>20330051920096</v>
       </c>
       <c r="B22" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C22" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="D22" t="s">
         <v>132</v>
@@ -4078,13 +4044,13 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23">
-        <v>20330051920095</v>
+        <v>20330051920097</v>
       </c>
       <c r="B23" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="C23" t="s">
-        <v>89</v>
+        <v>111</v>
       </c>
       <c r="D23" t="s">
         <v>133</v>
@@ -4095,13 +4061,10 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24">
-        <v>20330051920096</v>
+        <v>20330051920099</v>
       </c>
       <c r="B24" t="s">
-        <v>91</v>
-      </c>
-      <c r="C24" t="s">
-        <v>113</v>
+        <v>88</v>
       </c>
       <c r="D24" t="s">
         <v>134</v>
@@ -4115,10 +4078,10 @@
         <v>20330051920366</v>
       </c>
       <c r="B25" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="C25" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="D25" t="s">
         <v>135</v>
@@ -4132,10 +4095,10 @@
         <v>20330051920367</v>
       </c>
       <c r="B26" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="C26" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="D26" t="s">
         <v>136</v>
@@ -4149,10 +4112,10 @@
         <v>20330051920101</v>
       </c>
       <c r="B27" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C27" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D27" t="s">
         <v>137</v>
@@ -4166,10 +4129,10 @@
         <v>20330051920102</v>
       </c>
       <c r="B28" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="C28" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="D28" t="s">
         <v>138</v>
@@ -4183,10 +4146,10 @@
         <v>20330051920104</v>
       </c>
       <c r="B29" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="C29" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="D29" t="s">
         <v>139</v>
@@ -4200,10 +4163,10 @@
         <v>20330051920105</v>
       </c>
       <c r="B30" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="C30" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="D30" t="s">
         <v>140</v>
@@ -4217,10 +4180,10 @@
         <v>20330051920109</v>
       </c>
       <c r="B31" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C31" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="D31" t="s">
         <v>141</v>
@@ -4234,10 +4197,10 @@
         <v>20330051920111</v>
       </c>
       <c r="B32" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C32" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D32" t="s">
         <v>142</v>
@@ -4251,10 +4214,10 @@
         <v>20330051920112</v>
       </c>
       <c r="B33" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="C33" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D33" t="s">
         <v>143</v>
@@ -4270,7 +4233,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4305,19 +4268,19 @@
         <v>20330051920039</v>
       </c>
       <c r="B2" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="C2" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="D2" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="E2" t="s">
         <v>5</v>
       </c>
       <c r="F2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -4328,13 +4291,13 @@
         <v>20330051920039</v>
       </c>
       <c r="B3" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="C3" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="D3" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="E3" t="s">
         <v>6</v>
@@ -4351,13 +4314,13 @@
         <v>20330051920050</v>
       </c>
       <c r="B4" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="C4" t="s">
-        <v>62</v>
+        <v>87</v>
       </c>
       <c r="D4" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="E4" t="s">
         <v>6</v>
@@ -4374,19 +4337,19 @@
         <v>20330051920050</v>
       </c>
       <c r="B5" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="C5" t="s">
-        <v>62</v>
+        <v>87</v>
       </c>
       <c r="D5" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -4397,13 +4360,13 @@
         <v>20330051920100</v>
       </c>
       <c r="B6" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C6" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="D6" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="E6" t="s">
         <v>6</v>
@@ -4420,19 +4383,19 @@
         <v>20330051920100</v>
       </c>
       <c r="B7" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C7" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="D7" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="E7" t="s">
         <v>10</v>
       </c>
       <c r="F7" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="G7">
         <v>-1</v>
@@ -4443,13 +4406,13 @@
         <v>20330051920042</v>
       </c>
       <c r="B8" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="C8" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="D8" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="E8" t="s">
         <v>6</v>
@@ -4466,13 +4429,13 @@
         <v>20330051920046</v>
       </c>
       <c r="B9" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="C9" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="D9" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="E9" t="s">
         <v>6</v>
@@ -4489,13 +4452,13 @@
         <v>20330051920052</v>
       </c>
       <c r="B10" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="C10" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="D10" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E10" t="s">
         <v>6</v>
@@ -4509,19 +4472,22 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>20330051920099</v>
+        <v>20330051920107</v>
       </c>
       <c r="B11" t="s">
         <v>63</v>
       </c>
+      <c r="C11" t="s">
+        <v>63</v>
+      </c>
       <c r="D11" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="E11" t="s">
         <v>10</v>
       </c>
       <c r="F11" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="G11">
         <v>-1</v>
@@ -4529,47 +4495,24 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>20330051920107</v>
+        <v>20330051920113</v>
       </c>
       <c r="B12" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C12" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D12" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="E12" t="s">
         <v>10</v>
       </c>
       <c r="F12" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="G12">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>20330051920113</v>
-      </c>
-      <c r="B13" t="s">
-        <v>66</v>
-      </c>
-      <c r="C13" t="s">
-        <v>69</v>
-      </c>
-      <c r="D13" t="s">
-        <v>74</v>
-      </c>
-      <c r="E13" t="s">
-        <v>10</v>
-      </c>
-      <c r="F13" t="s">
-        <v>53</v>
-      </c>
-      <c r="G13">
         <v>-1</v>
       </c>
     </row>

--- a/grupos/3BEM - Estadisticos 20211.xlsx
+++ b/grupos/3BEM - Estadisticos 20211.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="144">
   <si>
     <t>Materia</t>
   </si>
@@ -176,21 +176,21 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>Avila Coronado Julieta</t>
+  </si>
+  <si>
     <t>Rodríguez Román Leticia</t>
   </si>
   <si>
+    <t>Molina Quezada Raúl</t>
+  </si>
+  <si>
+    <t>Camarillo Aburto Raymundo</t>
+  </si>
+  <si>
     <t>Cruz Alejo José Armando</t>
   </si>
   <si>
-    <t>Avila Coronado Julieta</t>
-  </si>
-  <si>
-    <t>Camarillo Aburto Raymundo</t>
-  </si>
-  <si>
-    <t>Molina Quezada Raúl</t>
-  </si>
-  <si>
     <t>Aurioles Maldonado Luis Gustavo</t>
   </si>
   <si>
@@ -206,250 +206,250 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>ALVAREZ</t>
+  </si>
+  <si>
+    <t>AMADOR</t>
+  </si>
+  <si>
+    <t>ANASTACIO</t>
+  </si>
+  <si>
+    <t>AGUILAR</t>
+  </si>
+  <si>
+    <t>BERNARDO</t>
+  </si>
+  <si>
+    <t>CITALAN</t>
+  </si>
+  <si>
+    <t>CID</t>
+  </si>
+  <si>
+    <t>COLOHUA</t>
+  </si>
+  <si>
+    <t>DE LA CRUZ</t>
+  </si>
+  <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>DIAZ</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>GOMEZ</t>
+  </si>
+  <si>
+    <t>GUEVARA</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>DE JESUS</t>
+  </si>
+  <si>
+    <t>MENDIZABAL</t>
+  </si>
+  <si>
+    <t>NAJERA</t>
+  </si>
+  <si>
     <t>NUBE</t>
   </si>
   <si>
+    <t>ORTIZ</t>
+  </si>
+  <si>
+    <t>OLMOS</t>
+  </si>
+  <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
     <t>SANCHEZ</t>
   </si>
   <si>
+    <t>TELLEZ</t>
+  </si>
+  <si>
+    <t>VALENTE</t>
+  </si>
+  <si>
+    <t>VASQUEZ</t>
+  </si>
+  <si>
     <t>XOTLANIHUA</t>
   </si>
   <si>
+    <t>CONCHE</t>
+  </si>
+  <si>
+    <t>PORRAS</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>GARCÍA</t>
+  </si>
+  <si>
+    <t>CONCHOA</t>
+  </si>
+  <si>
+    <t>ROMANOS</t>
+  </si>
+  <si>
+    <t>VALENCIA</t>
+  </si>
+  <si>
+    <t>MARROQUIN</t>
+  </si>
+  <si>
+    <t>VAZQUEZ</t>
+  </si>
+  <si>
+    <t>SEGURA</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>HERRERA</t>
+  </si>
+  <si>
+    <t>VELAZQUEZ</t>
+  </si>
+  <si>
+    <t>MARCELINO</t>
+  </si>
+  <si>
+    <t>EVARISTO</t>
+  </si>
+  <si>
     <t>ALEMAN</t>
   </si>
   <si>
+    <t>ROSETE</t>
+  </si>
+  <si>
+    <t>ROBLES</t>
+  </si>
+  <si>
+    <t>GAMEZ</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
     <t>TEXCAHUA</t>
   </si>
   <si>
+    <t>GUSTAVO</t>
+  </si>
+  <si>
+    <t>FRANCISCO ALAN</t>
+  </si>
+  <si>
+    <t>HIRAM FABIAN</t>
+  </si>
+  <si>
+    <t>RAUL</t>
+  </si>
+  <si>
+    <t>URIEL</t>
+  </si>
+  <si>
+    <t>MISAEL</t>
+  </si>
+  <si>
+    <t>JESUS</t>
+  </si>
+  <si>
+    <t>DAVID</t>
+  </si>
+  <si>
+    <t>YAHIR</t>
+  </si>
+  <si>
+    <t>BRUNO AZAEL</t>
+  </si>
+  <si>
+    <t>CESAR</t>
+  </si>
+  <si>
+    <t>MARIA ASUNCION</t>
+  </si>
+  <si>
+    <t>MARCO ANTONIO</t>
+  </si>
+  <si>
+    <t>ROBERTO</t>
+  </si>
+  <si>
+    <t>NOEL ALBERTO</t>
+  </si>
+  <si>
+    <t>LUIS ALBERTO</t>
+  </si>
+  <si>
+    <t>ADRIAN</t>
+  </si>
+  <si>
+    <t>ALDAIR ALAN</t>
+  </si>
+  <si>
+    <t>ALDER ALBERTO</t>
+  </si>
+  <si>
+    <t>ELI ANTONIO</t>
+  </si>
+  <si>
+    <t>ISAAC</t>
+  </si>
+  <si>
     <t>CHRISTIAN YAIR</t>
   </si>
   <si>
+    <t>SERGIO MARIANO</t>
+  </si>
+  <si>
+    <t>IVAN</t>
+  </si>
+  <si>
+    <t>JUAN CARLOS</t>
+  </si>
+  <si>
+    <t>CESAR OMAR</t>
+  </si>
+  <si>
     <t>ROSA ISELA</t>
   </si>
   <si>
+    <t>BENY ALEXANDER</t>
+  </si>
+  <si>
+    <t>ABIUD</t>
+  </si>
+  <si>
+    <t>GUILLERMO</t>
+  </si>
+  <si>
     <t>ALEXANDER</t>
-  </si>
-  <si>
-    <t>ALVAREZ</t>
-  </si>
-  <si>
-    <t>AMADOR</t>
-  </si>
-  <si>
-    <t>ANASTACIO</t>
-  </si>
-  <si>
-    <t>AGUILAR</t>
-  </si>
-  <si>
-    <t>BERNARDO</t>
-  </si>
-  <si>
-    <t>CITALAN</t>
-  </si>
-  <si>
-    <t>CID</t>
-  </si>
-  <si>
-    <t>COLOHUA</t>
-  </si>
-  <si>
-    <t>DE LA CRUZ</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>DIAZ</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>GOMEZ</t>
-  </si>
-  <si>
-    <t>GUEVARA</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>DE JESUS</t>
-  </si>
-  <si>
-    <t>MENDIZABAL</t>
-  </si>
-  <si>
-    <t>NAJERA</t>
-  </si>
-  <si>
-    <t>ORTIZ</t>
-  </si>
-  <si>
-    <t>OLMOS</t>
-  </si>
-  <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>TELLEZ</t>
-  </si>
-  <si>
-    <t>VALENTE</t>
-  </si>
-  <si>
-    <t>VASQUEZ</t>
-  </si>
-  <si>
-    <t>CONCHE</t>
-  </si>
-  <si>
-    <t>PORRAS</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>GARCÍA</t>
-  </si>
-  <si>
-    <t>CONCHOA</t>
-  </si>
-  <si>
-    <t>ROMANOS</t>
-  </si>
-  <si>
-    <t>VALENCIA</t>
-  </si>
-  <si>
-    <t>MARROQUIN</t>
-  </si>
-  <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
-    <t>SEGURA</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>HERRERA</t>
-  </si>
-  <si>
-    <t>VELAZQUEZ</t>
-  </si>
-  <si>
-    <t>MARCELINO</t>
-  </si>
-  <si>
-    <t>EVARISTO</t>
-  </si>
-  <si>
-    <t>ROSETE</t>
-  </si>
-  <si>
-    <t>ROBLES</t>
-  </si>
-  <si>
-    <t>GAMEZ</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>GUSTAVO</t>
-  </si>
-  <si>
-    <t>FRANCISCO ALAN</t>
-  </si>
-  <si>
-    <t>HIRAM FABIAN</t>
-  </si>
-  <si>
-    <t>RAUL</t>
-  </si>
-  <si>
-    <t>URIEL</t>
-  </si>
-  <si>
-    <t>MISAEL</t>
-  </si>
-  <si>
-    <t>JESUS</t>
-  </si>
-  <si>
-    <t>DAVID</t>
-  </si>
-  <si>
-    <t>YAHIR</t>
-  </si>
-  <si>
-    <t>BRUNO AZAEL</t>
-  </si>
-  <si>
-    <t>CESAR</t>
-  </si>
-  <si>
-    <t>MARIA ASUNCION</t>
-  </si>
-  <si>
-    <t>MARCO ANTONIO</t>
-  </si>
-  <si>
-    <t>ROBERTO</t>
-  </si>
-  <si>
-    <t>NOEL ALBERTO</t>
-  </si>
-  <si>
-    <t>LUIS ALBERTO</t>
-  </si>
-  <si>
-    <t>ADRIAN</t>
-  </si>
-  <si>
-    <t>ALDAIR ALAN</t>
-  </si>
-  <si>
-    <t>ALDER ALBERTO</t>
-  </si>
-  <si>
-    <t>ELI ANTONIO</t>
-  </si>
-  <si>
-    <t>ISAAC</t>
-  </si>
-  <si>
-    <t>SERGIO MARIANO</t>
-  </si>
-  <si>
-    <t>IVAN</t>
-  </si>
-  <si>
-    <t>JUAN CARLOS</t>
-  </si>
-  <si>
-    <t>CESAR OMAR</t>
-  </si>
-  <si>
-    <t>BENY ALEXANDER</t>
-  </si>
-  <si>
-    <t>ABIUD</t>
-  </si>
-  <si>
-    <t>GUILLERMO</t>
   </si>
 </sst>
 </file>
@@ -971,31 +971,31 @@
         <v>9</v>
       </c>
       <c r="N4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T4">
         <v>8</v>
       </c>
       <c r="U4">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V4">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W4">
         <v>8</v>
@@ -1004,7 +1004,7 @@
         <v>10</v>
       </c>
       <c r="Y4">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:25">
@@ -1033,7 +1033,7 @@
         <v>5</v>
       </c>
       <c r="I5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J5">
         <v>8</v>
@@ -1048,31 +1048,31 @@
         <v>9</v>
       </c>
       <c r="N5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V5">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W5">
         <v>8</v>
@@ -1081,7 +1081,7 @@
         <v>9</v>
       </c>
       <c r="Y5">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:25">
@@ -1125,22 +1125,22 @@
         <v>9</v>
       </c>
       <c r="N6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T6">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>6</v>
       </c>
       <c r="V6">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W6">
         <v>7</v>
@@ -1158,7 +1158,7 @@
         <v>10</v>
       </c>
       <c r="Y6">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7" spans="1:25">
@@ -1202,22 +1202,22 @@
         <v>8</v>
       </c>
       <c r="N7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T7">
         <v>6</v>
@@ -1226,7 +1226,7 @@
         <v>5</v>
       </c>
       <c r="V7">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W7">
         <v>7</v>
@@ -1235,7 +1235,7 @@
         <v>10</v>
       </c>
       <c r="Y7">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8" spans="1:25">
@@ -1279,31 +1279,31 @@
         <v>8</v>
       </c>
       <c r="N8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T8">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U8">
         <v>6</v>
       </c>
       <c r="V8">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="W8">
         <v>7</v>
@@ -1312,7 +1312,7 @@
         <v>10</v>
       </c>
       <c r="Y8">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9" spans="1:25">
@@ -1341,7 +1341,7 @@
         <v>10</v>
       </c>
       <c r="I9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J9">
         <v>9</v>
@@ -1356,28 +1356,28 @@
         <v>8</v>
       </c>
       <c r="N9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T9">
         <v>8</v>
       </c>
       <c r="U9">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V9">
         <v>9</v>
@@ -1389,7 +1389,7 @@
         <v>10</v>
       </c>
       <c r="Y9">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10" spans="1:25">
@@ -1433,22 +1433,22 @@
         <v>9</v>
       </c>
       <c r="N10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T10">
         <v>10</v>
@@ -1466,7 +1466,7 @@
         <v>10</v>
       </c>
       <c r="Y10">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="11" spans="1:25">
@@ -1510,22 +1510,22 @@
         <v>9</v>
       </c>
       <c r="N11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T11">
         <v>10</v>
@@ -1534,7 +1534,7 @@
         <v>7</v>
       </c>
       <c r="V11">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W11">
         <v>8</v>
@@ -1543,7 +1543,7 @@
         <v>10</v>
       </c>
       <c r="Y11">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12" spans="1:25">
@@ -1587,22 +1587,22 @@
         <v>9</v>
       </c>
       <c r="N12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T12">
         <v>10</v>
@@ -1620,7 +1620,7 @@
         <v>10</v>
       </c>
       <c r="Y12">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13" spans="1:25">
@@ -1649,7 +1649,7 @@
         <v>6</v>
       </c>
       <c r="I13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J13">
         <v>5</v>
@@ -1664,40 +1664,40 @@
         <v>8</v>
       </c>
       <c r="N13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T13">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U13">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V13">
         <v>5</v>
       </c>
       <c r="W13">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X13">
         <v>10</v>
       </c>
       <c r="Y13">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="14" spans="1:25">
@@ -1741,40 +1741,40 @@
         <v>8</v>
       </c>
       <c r="N14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X14">
         <v>10</v>
       </c>
       <c r="Y14">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="15" spans="1:25">
@@ -1818,31 +1818,31 @@
         <v>9</v>
       </c>
       <c r="N15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T15">
         <v>8</v>
       </c>
       <c r="U15">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V15">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W15">
         <v>7</v>
@@ -1851,7 +1851,7 @@
         <v>10</v>
       </c>
       <c r="Y15">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="16" spans="1:25">
@@ -1880,7 +1880,7 @@
         <v>7</v>
       </c>
       <c r="I16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J16">
         <v>6</v>
@@ -1895,31 +1895,31 @@
         <v>7</v>
       </c>
       <c r="N16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T16">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U16">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V16">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W16">
         <v>7</v>
@@ -1928,7 +1928,7 @@
         <v>9</v>
       </c>
       <c r="Y16">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17" spans="1:25">
@@ -1972,31 +1972,31 @@
         <v>10</v>
       </c>
       <c r="N17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T17">
         <v>9</v>
       </c>
       <c r="U17">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V17">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W17">
         <v>10</v>
@@ -2049,31 +2049,31 @@
         <v>9</v>
       </c>
       <c r="N18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T18">
         <v>10</v>
       </c>
       <c r="U18">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V18">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W18">
         <v>8</v>
@@ -2082,7 +2082,7 @@
         <v>10</v>
       </c>
       <c r="Y18">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="19" spans="1:25">
@@ -2126,31 +2126,31 @@
         <v>7</v>
       </c>
       <c r="N19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T19">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U19">
         <v>6</v>
       </c>
       <c r="V19">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W19">
         <v>7</v>
@@ -2159,7 +2159,7 @@
         <v>10</v>
       </c>
       <c r="Y19">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20" spans="1:25">
@@ -2188,7 +2188,7 @@
         <v>10</v>
       </c>
       <c r="I20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J20">
         <v>9</v>
@@ -2203,28 +2203,28 @@
         <v>9</v>
       </c>
       <c r="N20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T20">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U20">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V20">
         <v>9</v>
@@ -2236,7 +2236,7 @@
         <v>10</v>
       </c>
       <c r="Y20">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="21" spans="1:25">
@@ -2280,22 +2280,22 @@
         <v>9</v>
       </c>
       <c r="N21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T21">
         <v>9</v>
@@ -2313,7 +2313,7 @@
         <v>10</v>
       </c>
       <c r="Y21">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="22" spans="1:25">
@@ -2357,28 +2357,28 @@
         <v>8</v>
       </c>
       <c r="N22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T22">
         <v>10</v>
       </c>
       <c r="U22">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V22">
         <v>10</v>
@@ -2390,7 +2390,7 @@
         <v>10</v>
       </c>
       <c r="Y22">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="23" spans="1:25">
@@ -2419,7 +2419,7 @@
         <v>6</v>
       </c>
       <c r="I23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J23">
         <v>5</v>
@@ -2434,40 +2434,40 @@
         <v>8</v>
       </c>
       <c r="N23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T23">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U23">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V23">
         <v>5</v>
       </c>
       <c r="W23">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X23">
         <v>6</v>
       </c>
       <c r="Y23">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="24" spans="1:25">
@@ -2496,7 +2496,7 @@
         <v>5</v>
       </c>
       <c r="I24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J24">
         <v>5</v>
@@ -2511,40 +2511,40 @@
         <v>6</v>
       </c>
       <c r="N24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T24">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U24">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V24">
         <v>5</v>
       </c>
       <c r="W24">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X24">
         <v>6</v>
       </c>
       <c r="Y24">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="25" spans="1:25">
@@ -2567,13 +2567,13 @@
         <v>6</v>
       </c>
       <c r="G25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="H25">
         <v>6</v>
       </c>
       <c r="I25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J25">
         <v>6</v>
@@ -2585,25 +2585,25 @@
         <v>6</v>
       </c>
       <c r="M25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T25">
         <v>7</v>
@@ -2612,7 +2612,7 @@
         <v>5</v>
       </c>
       <c r="V25">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W25">
         <v>8</v>
@@ -2621,7 +2621,7 @@
         <v>6</v>
       </c>
       <c r="Y25">
-        <v>-1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="26" spans="1:25">
@@ -2662,34 +2662,34 @@
         <v>8</v>
       </c>
       <c r="M26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T26">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U26">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V26">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W26">
         <v>9</v>
@@ -2698,7 +2698,7 @@
         <v>8</v>
       </c>
       <c r="Y26">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="27" spans="1:25">
@@ -2742,31 +2742,31 @@
         <v>9</v>
       </c>
       <c r="N27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T27">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U27">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V27">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W27">
         <v>9</v>
@@ -2775,7 +2775,7 @@
         <v>10</v>
       </c>
       <c r="Y27">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="28" spans="1:25">
@@ -2819,40 +2819,40 @@
         <v>9</v>
       </c>
       <c r="N28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T28">
         <v>9</v>
       </c>
       <c r="U28">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V28">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W28">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X28">
         <v>10</v>
       </c>
       <c r="Y28">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="29" spans="1:25">
@@ -2896,31 +2896,31 @@
         <v>9</v>
       </c>
       <c r="N29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T29">
         <v>9</v>
       </c>
       <c r="U29">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V29">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W29">
         <v>10</v>
@@ -2929,7 +2929,7 @@
         <v>10</v>
       </c>
       <c r="Y29">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="30" spans="1:25">
@@ -2952,7 +2952,7 @@
         <v>8</v>
       </c>
       <c r="G30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="H30">
         <v>7</v>
@@ -2970,34 +2970,34 @@
         <v>8</v>
       </c>
       <c r="M30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T30">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U30">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V30">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W30">
         <v>8</v>
@@ -3006,7 +3006,7 @@
         <v>8</v>
       </c>
       <c r="Y30">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="31" spans="1:25">
@@ -3035,7 +3035,7 @@
         <v>6</v>
       </c>
       <c r="I31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J31">
         <v>5</v>
@@ -3047,25 +3047,25 @@
         <v>6</v>
       </c>
       <c r="M31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T31">
         <v>6</v>
@@ -3077,13 +3077,13 @@
         <v>5</v>
       </c>
       <c r="W31">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X31">
         <v>6</v>
       </c>
       <c r="Y31">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="32" spans="1:25">
@@ -3127,22 +3127,22 @@
         <v>9</v>
       </c>
       <c r="N32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T32">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>6</v>
       </c>
       <c r="V32">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W32">
         <v>9</v>
@@ -3160,7 +3160,7 @@
         <v>10</v>
       </c>
       <c r="Y32">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="33" spans="1:25">
@@ -3204,22 +3204,22 @@
         <v>8</v>
       </c>
       <c r="N33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T33">
         <v>9</v>
@@ -3228,7 +3228,7 @@
         <v>7</v>
       </c>
       <c r="V33">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W33">
         <v>8</v>
@@ -3237,7 +3237,7 @@
         <v>10</v>
       </c>
       <c r="Y33">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="34" spans="1:25">
@@ -3260,7 +3260,7 @@
         <v>8</v>
       </c>
       <c r="G34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="H34">
         <v>10</v>
@@ -3278,34 +3278,34 @@
         <v>10</v>
       </c>
       <c r="M34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T34">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U34">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V34">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="W34">
         <v>8</v>
@@ -3314,7 +3314,7 @@
         <v>9</v>
       </c>
       <c r="Y34">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -3370,7 +3370,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B2" t="s">
         <v>52</v>
@@ -3379,19 +3379,19 @@
         <v>32</v>
       </c>
       <c r="D2">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="E2">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F2">
-        <v>68.75</v>
+        <v>81.25</v>
       </c>
       <c r="G2">
-        <v>31.25</v>
+        <v>18.75</v>
       </c>
       <c r="H2">
-        <v>6.4</v>
+        <v>7.5</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -3402,7 +3402,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B3" t="s">
         <v>53</v>
@@ -3411,19 +3411,19 @@
         <v>32</v>
       </c>
       <c r="D3">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F3">
-        <v>84.38</v>
+        <v>87.5</v>
       </c>
       <c r="G3">
-        <v>15.63</v>
+        <v>12.5</v>
       </c>
       <c r="H3">
-        <v>7.7</v>
+        <v>6.3</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -3434,7 +3434,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B4" t="s">
         <v>54</v>
@@ -3443,19 +3443,19 @@
         <v>32</v>
       </c>
       <c r="D4">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="E4">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F4">
-        <v>87.5</v>
+        <v>100</v>
       </c>
       <c r="G4">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="H4">
-        <v>8</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -3475,19 +3475,19 @@
         <v>32</v>
       </c>
       <c r="D5">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="E5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F5">
-        <v>87.5</v>
+        <v>100</v>
       </c>
       <c r="G5">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="H5">
-        <v>7.8</v>
+        <v>8.1</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -3498,7 +3498,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B6" t="s">
         <v>56</v>
@@ -3507,25 +3507,25 @@
         <v>32</v>
       </c>
       <c r="D6">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E6">
         <v>0</v>
       </c>
       <c r="F6">
-        <v>90.63</v>
+        <v>100</v>
       </c>
       <c r="G6">
         <v>0</v>
       </c>
       <c r="H6">
-        <v>9.4</v>
+        <v>7.8</v>
       </c>
       <c r="I6">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J6">
-        <v>9.380000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -3567,7 +3567,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -3592,66 +3592,6 @@
       </c>
       <c r="F1" s="1" t="s">
         <v>11</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="A2">
-        <v>20330051920100</v>
-      </c>
-      <c r="B2" t="s">
-        <v>62</v>
-      </c>
-      <c r="C2" t="s">
-        <v>65</v>
-      </c>
-      <c r="D2" t="s">
-        <v>67</v>
-      </c>
-      <c r="E2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F2" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3">
-        <v>20330051920107</v>
-      </c>
-      <c r="B3" t="s">
-        <v>63</v>
-      </c>
-      <c r="C3" t="s">
-        <v>63</v>
-      </c>
-      <c r="D3" t="s">
-        <v>68</v>
-      </c>
-      <c r="E3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F3" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4">
-        <v>20330051920113</v>
-      </c>
-      <c r="B4" t="s">
-        <v>64</v>
-      </c>
-      <c r="C4" t="s">
-        <v>66</v>
-      </c>
-      <c r="D4" t="s">
-        <v>69</v>
-      </c>
-      <c r="E4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F4" t="s">
-        <v>56</v>
       </c>
     </row>
   </sheetData>
@@ -3687,64 +3627,64 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2">
-        <v>20330051920100</v>
+        <v>20330051920039</v>
       </c>
       <c r="B2" t="s">
         <v>62</v>
       </c>
       <c r="C2" t="s">
-        <v>65</v>
+        <v>92</v>
       </c>
       <c r="D2" t="s">
-        <v>67</v>
+        <v>113</v>
       </c>
       <c r="E2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3">
-        <v>20330051920107</v>
+        <v>20330051920040</v>
       </c>
       <c r="B3" t="s">
         <v>63</v>
       </c>
       <c r="C3" t="s">
-        <v>63</v>
+        <v>93</v>
       </c>
       <c r="D3" t="s">
-        <v>68</v>
+        <v>114</v>
       </c>
       <c r="E3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>20330051920113</v>
+        <v>20330051920042</v>
       </c>
       <c r="B4" t="s">
         <v>64</v>
       </c>
       <c r="C4" t="s">
-        <v>66</v>
+        <v>94</v>
       </c>
       <c r="D4" t="s">
-        <v>69</v>
+        <v>115</v>
       </c>
       <c r="E4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>20330051920039</v>
+        <v>20330051920043</v>
       </c>
       <c r="B5" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="C5" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="D5" t="s">
         <v>116</v>
@@ -3755,13 +3695,13 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>20330051920040</v>
+        <v>20330051920044</v>
       </c>
       <c r="B6" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="C6" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D6" t="s">
         <v>117</v>
@@ -3772,13 +3712,13 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>20330051920042</v>
+        <v>20330051920045</v>
       </c>
       <c r="B7" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="C7" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="D7" t="s">
         <v>118</v>
@@ -3789,13 +3729,13 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>20330051920043</v>
+        <v>20330051920046</v>
       </c>
       <c r="B8" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="C8" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D8" t="s">
         <v>119</v>
@@ -3806,13 +3746,13 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>20330051920044</v>
+        <v>20330051920048</v>
       </c>
       <c r="B9" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="C9" t="s">
-        <v>101</v>
+        <v>75</v>
       </c>
       <c r="D9" t="s">
         <v>120</v>
@@ -3823,13 +3763,13 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>20330051920045</v>
+        <v>20330051920050</v>
       </c>
       <c r="B10" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="C10" t="s">
-        <v>102</v>
+        <v>79</v>
       </c>
       <c r="D10" t="s">
         <v>121</v>
@@ -3840,16 +3780,16 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>20330051920046</v>
+        <v>20330051920051</v>
       </c>
       <c r="B11" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="C11" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="D11" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="E11">
         <v>0</v>
@@ -3857,16 +3797,16 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>20330051920048</v>
+        <v>20330051920365</v>
       </c>
       <c r="B12" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="C12" t="s">
-        <v>83</v>
+        <v>100</v>
       </c>
       <c r="D12" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E12">
         <v>0</v>
@@ -3874,16 +3814,16 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>20330051920050</v>
+        <v>20330051920052</v>
       </c>
       <c r="B13" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="C13" t="s">
-        <v>87</v>
+        <v>101</v>
       </c>
       <c r="D13" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E13">
         <v>0</v>
@@ -3891,16 +3831,16 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>20330051920051</v>
+        <v>20330051920053</v>
       </c>
       <c r="B14" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="C14" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="D14" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="E14">
         <v>0</v>
@@ -3908,13 +3848,13 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>20330051920365</v>
+        <v>20330051920055</v>
       </c>
       <c r="B15" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="C15" t="s">
-        <v>105</v>
+        <v>73</v>
       </c>
       <c r="D15" t="s">
         <v>125</v>
@@ -3925,13 +3865,13 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>20330051920052</v>
+        <v>20330051920056</v>
       </c>
       <c r="B16" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="C16" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="D16" t="s">
         <v>126</v>
@@ -3942,13 +3882,13 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>20330051920053</v>
+        <v>20330051920057</v>
       </c>
       <c r="B17" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="C17" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="D17" t="s">
         <v>127</v>
@@ -3959,13 +3899,13 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>20330051920055</v>
+        <v>20330051920095</v>
       </c>
       <c r="B18" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="C18" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="D18" t="s">
         <v>128</v>
@@ -3976,13 +3916,13 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>20330051920056</v>
+        <v>20330051920096</v>
       </c>
       <c r="B19" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="C19" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="D19" t="s">
         <v>129</v>
@@ -3993,13 +3933,13 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>20330051920057</v>
+        <v>20330051920097</v>
       </c>
       <c r="B20" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="C20" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="D20" t="s">
         <v>130</v>
@@ -4010,13 +3950,10 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21">
-        <v>20330051920095</v>
+        <v>20330051920099</v>
       </c>
       <c r="B21" t="s">
-        <v>85</v>
-      </c>
-      <c r="C21" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="D21" t="s">
         <v>131</v>
@@ -4027,13 +3964,13 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22">
-        <v>20330051920096</v>
+        <v>20330051920366</v>
       </c>
       <c r="B22" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="C22" t="s">
-        <v>110</v>
+        <v>75</v>
       </c>
       <c r="D22" t="s">
         <v>132</v>
@@ -4044,13 +3981,13 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23">
-        <v>20330051920097</v>
+        <v>20330051920367</v>
       </c>
       <c r="B23" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="C23" t="s">
-        <v>111</v>
+        <v>75</v>
       </c>
       <c r="D23" t="s">
         <v>133</v>
@@ -4061,10 +3998,13 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24">
-        <v>20330051920099</v>
+        <v>20330051920100</v>
       </c>
       <c r="B24" t="s">
-        <v>88</v>
+        <v>82</v>
+      </c>
+      <c r="C24" t="s">
+        <v>107</v>
       </c>
       <c r="D24" t="s">
         <v>134</v>
@@ -4075,13 +4015,13 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25">
-        <v>20330051920366</v>
+        <v>20330051920101</v>
       </c>
       <c r="B25" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="C25" t="s">
-        <v>83</v>
+        <v>108</v>
       </c>
       <c r="D25" t="s">
         <v>135</v>
@@ -4092,13 +4032,13 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26">
-        <v>20330051920367</v>
+        <v>20330051920102</v>
       </c>
       <c r="B26" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="C26" t="s">
-        <v>83</v>
+        <v>109</v>
       </c>
       <c r="D26" t="s">
         <v>136</v>
@@ -4109,13 +4049,13 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27">
-        <v>20330051920101</v>
+        <v>20330051920104</v>
       </c>
       <c r="B27" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="C27" t="s">
-        <v>112</v>
+        <v>102</v>
       </c>
       <c r="D27" t="s">
         <v>137</v>
@@ -4126,13 +4066,13 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28">
-        <v>20330051920102</v>
+        <v>20330051920105</v>
       </c>
       <c r="B28" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="C28" t="s">
-        <v>113</v>
+        <v>78</v>
       </c>
       <c r="D28" t="s">
         <v>138</v>
@@ -4143,13 +4083,13 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29">
-        <v>20330051920104</v>
+        <v>20330051920107</v>
       </c>
       <c r="B29" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="C29" t="s">
-        <v>107</v>
+        <v>87</v>
       </c>
       <c r="D29" t="s">
         <v>139</v>
@@ -4160,13 +4100,13 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30">
-        <v>20330051920105</v>
+        <v>20330051920109</v>
       </c>
       <c r="B30" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="C30" t="s">
-        <v>86</v>
+        <v>98</v>
       </c>
       <c r="D30" t="s">
         <v>140</v>
@@ -4177,13 +4117,13 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31">
-        <v>20330051920109</v>
+        <v>20330051920111</v>
       </c>
       <c r="B31" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="C31" t="s">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="D31" t="s">
         <v>141</v>
@@ -4194,13 +4134,13 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32">
-        <v>20330051920111</v>
+        <v>20330051920112</v>
       </c>
       <c r="B32" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="C32" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="D32" t="s">
         <v>142</v>
@@ -4211,13 +4151,13 @@
     </row>
     <row r="33" spans="1:5">
       <c r="A33">
-        <v>20330051920112</v>
+        <v>20330051920113</v>
       </c>
       <c r="B33" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="C33" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="D33" t="s">
         <v>143</v>
@@ -4233,7 +4173,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4265,22 +4205,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>20330051920039</v>
+        <v>20330051920100</v>
       </c>
       <c r="B2" t="s">
-        <v>70</v>
+        <v>82</v>
       </c>
       <c r="C2" t="s">
-        <v>97</v>
+        <v>107</v>
       </c>
       <c r="D2" t="s">
-        <v>116</v>
+        <v>134</v>
       </c>
       <c r="E2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F2" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -4288,19 +4228,19 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>20330051920039</v>
+        <v>20330051920100</v>
       </c>
       <c r="B3" t="s">
-        <v>70</v>
+        <v>82</v>
       </c>
       <c r="C3" t="s">
-        <v>97</v>
+        <v>107</v>
       </c>
       <c r="D3" t="s">
-        <v>116</v>
+        <v>134</v>
       </c>
       <c r="E3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F3" t="s">
         <v>52</v>
@@ -4311,22 +4251,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920050</v>
+        <v>20330051920109</v>
       </c>
       <c r="B4" t="s">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="C4" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="D4" t="s">
-        <v>124</v>
+        <v>140</v>
       </c>
       <c r="E4" t="s">
         <v>6</v>
       </c>
       <c r="F4" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -4334,22 +4274,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920050</v>
+        <v>20330051920109</v>
       </c>
       <c r="B5" t="s">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="C5" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="D5" t="s">
-        <v>124</v>
+        <v>140</v>
       </c>
       <c r="E5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -4357,22 +4297,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>20330051920100</v>
+        <v>20330051920042</v>
       </c>
       <c r="B6" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C6" t="s">
-        <v>65</v>
+        <v>94</v>
       </c>
       <c r="D6" t="s">
-        <v>67</v>
+        <v>115</v>
       </c>
       <c r="E6" t="s">
         <v>6</v>
       </c>
       <c r="F6" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -4380,42 +4320,42 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>20330051920100</v>
+        <v>20330051920052</v>
       </c>
       <c r="B7" t="s">
-        <v>62</v>
+        <v>73</v>
       </c>
       <c r="C7" t="s">
-        <v>65</v>
+        <v>101</v>
       </c>
       <c r="D7" t="s">
-        <v>67</v>
+        <v>123</v>
       </c>
       <c r="E7" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F7" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="G7">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>20330051920042</v>
+        <v>20330051920097</v>
       </c>
       <c r="B8" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="C8" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="D8" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
       <c r="E8" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F8" t="s">
         <v>52</v>
@@ -4426,22 +4366,19 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>20330051920046</v>
+        <v>20330051920099</v>
       </c>
       <c r="B9" t="s">
-        <v>76</v>
-      </c>
-      <c r="C9" t="s">
-        <v>103</v>
+        <v>80</v>
       </c>
       <c r="D9" t="s">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="E9" t="s">
         <v>6</v>
       </c>
       <c r="F9" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G9">
         <v>5</v>
@@ -4449,19 +4386,19 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>20330051920052</v>
+        <v>20330051920366</v>
       </c>
       <c r="B10" t="s">
         <v>81</v>
       </c>
       <c r="C10" t="s">
-        <v>106</v>
+        <v>75</v>
       </c>
       <c r="D10" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="E10" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F10" t="s">
         <v>52</v>
@@ -4472,48 +4409,25 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>20330051920107</v>
+        <v>20330051920367</v>
       </c>
       <c r="B11" t="s">
-        <v>63</v>
+        <v>81</v>
       </c>
       <c r="C11" t="s">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="D11" t="s">
-        <v>68</v>
+        <v>133</v>
       </c>
       <c r="E11" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F11" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="G11">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>20330051920113</v>
-      </c>
-      <c r="B12" t="s">
-        <v>64</v>
-      </c>
-      <c r="C12" t="s">
-        <v>66</v>
-      </c>
-      <c r="D12" t="s">
-        <v>69</v>
-      </c>
-      <c r="E12" t="s">
-        <v>10</v>
-      </c>
-      <c r="F12" t="s">
-        <v>56</v>
-      </c>
-      <c r="G12">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
